--- a/Analyses/Partner-Analyses-Metadata.xlsx
+++ b/Analyses/Partner-Analyses-Metadata.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LauraMerson/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/otss1968_ox_ac_uk/Documents/Documents/GitHub/CCP/Analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7DD31F5-77BB-0C4A-8A31-25D66420D0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{A7DD31F5-77BB-0C4A-8A31-25D66420D0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89875BCA-CA7C-4FAF-BC57-092575E41F64}"/>
   <bookViews>
-    <workbookView xWindow="-35200" yWindow="-6280" windowWidth="28900" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Partner Analyses" sheetId="1" r:id="rId1"/>
     <sheet name="Sub-processors" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="300">
   <si>
     <t>Short Title and Link to Proposal</t>
   </si>
@@ -1105,6 +1110,9 @@
   <si>
     <t>josephine.bourner@proton.me</t>
   </si>
+  <si>
+    <t>Omicron surge impact on acute kidney injury in ICU patients: A study using the ISARIC COVID-19 database | PLOS One</t>
+  </si>
 </sst>
 </file>
 
@@ -1572,7 +1580,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1743,18 +1751,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1763,30 +1791,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2007,34 +2028,34 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AB1003"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:AB1004"/>
+  <sheetFormatPr defaultColWidth="14.46484375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.5" customWidth="1"/>
+    <col min="1" max="1" width="27.46484375" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="24.1640625" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="5" width="31.5" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.1328125" customWidth="1"/>
+    <col min="4" max="4" width="24.46484375" customWidth="1"/>
+    <col min="5" max="5" width="31.46484375" customWidth="1"/>
+    <col min="6" max="6" width="15.796875" customWidth="1"/>
     <col min="7" max="7" width="76.33203125" customWidth="1"/>
-    <col min="8" max="8" width="25.5" customWidth="1"/>
-    <col min="9" max="9" width="30.1640625" customWidth="1"/>
-    <col min="10" max="10" width="29.5" customWidth="1"/>
+    <col min="8" max="8" width="25.46484375" customWidth="1"/>
+    <col min="9" max="9" width="30.1328125" customWidth="1"/>
+    <col min="10" max="10" width="29.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:28" ht="14.25">
+      <c r="A1" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -2054,17 +2075,17 @@
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
     </row>
-    <row r="2" spans="1:28">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
+    <row r="2" spans="1:28" ht="14.25">
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -2084,7 +2105,7 @@
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" ht="32">
+    <row r="3" spans="1:28" ht="28.5">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2162,10 +2183,10 @@
       <c r="G4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="81" t="s">
+      <c r="H4" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="63"/>
+      <c r="I4" s="69"/>
       <c r="J4" s="14" t="s">
         <v>19</v>
       </c>
@@ -2190,7 +2211,7 @@
       <c r="AA4" s="9"/>
       <c r="AB4" s="9"/>
     </row>
-    <row r="5" spans="1:28" ht="48">
+    <row r="5" spans="1:28" ht="42.75">
       <c r="A5" s="13" t="s">
         <v>21</v>
       </c>
@@ -2210,10 +2231,10 @@
       <c r="G5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="63"/>
+      <c r="I5" s="69"/>
       <c r="J5" s="14" t="s">
         <v>19</v>
       </c>
@@ -2238,7 +2259,7 @@
       <c r="AA5" s="9"/>
       <c r="AB5" s="9"/>
     </row>
-    <row r="6" spans="1:28" ht="64">
+    <row r="6" spans="1:28" ht="57">
       <c r="A6" s="20" t="s">
         <v>24</v>
       </c>
@@ -2291,10 +2312,10 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28" ht="50.25" customHeight="1">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="70" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -2309,13 +2330,13 @@
       <c r="F7" s="12">
         <v>44540</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="66" t="s">
+      <c r="H7" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="66" t="s">
+      <c r="I7" s="74" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="22" t="s">
@@ -2341,8 +2362,8 @@
       <c r="AB7" s="9"/>
     </row>
     <row r="8" spans="1:28" ht="30.75" customHeight="1">
-      <c r="A8" s="67"/>
-      <c r="B8" s="67"/>
+      <c r="A8" s="71"/>
+      <c r="B8" s="71"/>
       <c r="C8" s="10" t="s">
         <v>14</v>
       </c>
@@ -2355,9 +2376,9 @@
       <c r="F8" s="12">
         <v>44772</v>
       </c>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
       <c r="J8" s="22" t="s">
         <v>40</v>
       </c>
@@ -2381,8 +2402,8 @@
       <c r="AB8" s="9"/>
     </row>
     <row r="9" spans="1:28" ht="39.75" customHeight="1">
-      <c r="A9" s="67"/>
-      <c r="B9" s="67"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="10" t="s">
         <v>14</v>
       </c>
@@ -2395,9 +2416,9 @@
       <c r="F9" s="12">
         <v>44817</v>
       </c>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
       <c r="J9" s="22" t="s">
         <v>40</v>
       </c>
@@ -2421,8 +2442,8 @@
       <c r="AB9" s="9"/>
     </row>
     <row r="10" spans="1:28" ht="47.25" customHeight="1">
-      <c r="A10" s="65"/>
-      <c r="B10" s="65"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="72"/>
       <c r="C10" s="10" t="s">
         <v>14</v>
       </c>
@@ -2435,9 +2456,9 @@
       <c r="F10" s="12">
         <v>45055</v>
       </c>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
       <c r="J10" s="22" t="s">
         <v>40</v>
       </c>
@@ -2565,10 +2586,10 @@
       <c r="AB12" s="9"/>
     </row>
     <row r="13" spans="1:28" ht="66.75" customHeight="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="70" t="s">
         <v>57</v>
       </c>
       <c r="C13" s="31" t="s">
@@ -2583,16 +2604,16 @@
       <c r="F13" s="12">
         <v>44671</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="H13" s="64" t="s">
+      <c r="H13" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="66" t="s">
+      <c r="J13" s="74" t="s">
         <v>63</v>
       </c>
       <c r="K13" s="34">
@@ -2616,9 +2637,9 @@
       <c r="AA13" s="9"/>
       <c r="AB13" s="9"/>
     </row>
-    <row r="14" spans="1:28" ht="78.75" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
+    <row r="14" spans="1:28" s="62" customFormat="1" ht="66.75" customHeight="1">
+      <c r="A14" s="86"/>
+      <c r="B14" s="87"/>
       <c r="C14" s="10" t="s">
         <v>14</v>
       </c>
@@ -2631,10 +2652,10 @@
       <c r="F14" s="12">
         <v>45072</v>
       </c>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="89"/>
       <c r="K14" s="34"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2654,40 +2675,26 @@
       <c r="AA14" s="9"/>
       <c r="AB14" s="9"/>
     </row>
-    <row r="15" spans="1:28" ht="84" customHeight="1">
-      <c r="A15" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>66</v>
-      </c>
+    <row r="15" spans="1:28" s="62" customFormat="1" ht="66.75" customHeight="1">
+      <c r="A15" s="86"/>
+      <c r="B15" s="87"/>
       <c r="C15" s="31" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>68</v>
+        <v>299</v>
       </c>
       <c r="F15" s="12">
-        <v>44985</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="K15" s="36">
-        <v>44566</v>
-      </c>
+        <v>45981</v>
+      </c>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="34"/>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
       <c r="N15" s="9"/>
@@ -2706,39 +2713,39 @@
       <c r="AA15" s="9"/>
       <c r="AB15" s="9"/>
     </row>
-    <row r="16" spans="1:28" ht="45" customHeight="1">
-      <c r="A16" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="74" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="17" t="s">
+    <row r="16" spans="1:28" ht="84" customHeight="1">
+      <c r="A16" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="37" t="s">
-        <v>73</v>
+      <c r="E16" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F16" s="12">
-        <v>44814</v>
-      </c>
-      <c r="G16" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" s="34">
-        <v>44340</v>
+        <v>44985</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="36">
+        <v>44566</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
@@ -2758,32 +2765,40 @@
       <c r="AA16" s="9"/>
       <c r="AB16" s="9"/>
     </row>
-    <row r="17" spans="1:28" ht="102" customHeight="1">
-      <c r="A17" s="67"/>
-      <c r="B17" s="67"/>
+    <row r="17" spans="1:28" ht="45" customHeight="1">
+      <c r="A17" s="75" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>72</v>
+      </c>
       <c r="C17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="35" t="s">
-        <v>78</v>
+      <c r="E17" s="37" t="s">
+        <v>73</v>
       </c>
       <c r="F17" s="12">
-        <v>45331</v>
-      </c>
-      <c r="G17" s="67"/>
+        <v>44814</v>
+      </c>
+      <c r="G17" s="73" t="s">
+        <v>74</v>
+      </c>
       <c r="H17" s="24" t="s">
         <v>75</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J17" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="K17" s="34"/>
+      <c r="K17" s="34">
+        <v>44340</v>
+      </c>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="9"/>
@@ -2802,30 +2817,30 @@
       <c r="AA17" s="9"/>
       <c r="AB17" s="9"/>
     </row>
-    <row r="18" spans="1:28" ht="78" customHeight="1">
-      <c r="A18" s="67"/>
-      <c r="B18" s="65"/>
+    <row r="18" spans="1:28" ht="102" customHeight="1">
+      <c r="A18" s="71"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="37" t="s">
-        <v>79</v>
+      <c r="E18" s="35" t="s">
+        <v>78</v>
       </c>
       <c r="F18" s="12">
-        <v>45266</v>
-      </c>
-      <c r="G18" s="67"/>
+        <v>45331</v>
+      </c>
+      <c r="G18" s="71"/>
       <c r="H18" s="24" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J18" s="24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K18" s="34"/>
       <c r="L18" s="16"/>
@@ -2846,38 +2861,32 @@
       <c r="AA18" s="9"/>
       <c r="AB18" s="9"/>
     </row>
-    <row r="19" spans="1:28" ht="142.5" customHeight="1">
-      <c r="A19" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>83</v>
-      </c>
+    <row r="19" spans="1:28" ht="78" customHeight="1">
+      <c r="A19" s="71"/>
+      <c r="B19" s="72"/>
       <c r="C19" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="35" t="s">
-        <v>84</v>
+      <c r="E19" s="37" t="s">
+        <v>79</v>
       </c>
       <c r="F19" s="12">
-        <v>45107</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="K19" s="15"/>
+        <v>45266</v>
+      </c>
+      <c r="G19" s="71"/>
+      <c r="H19" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="34"/>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" s="9"/>
@@ -2896,36 +2905,36 @@
       <c r="AA19" s="9"/>
       <c r="AB19" s="9"/>
     </row>
-    <row r="20" spans="1:28" ht="112">
+    <row r="20" spans="1:28" ht="142.5" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>91</v>
+      <c r="E20" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="F20" s="12">
-        <v>45025</v>
+        <v>45107</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="16"/>
@@ -2946,40 +2955,38 @@
       <c r="AA20" s="9"/>
       <c r="AB20" s="9"/>
     </row>
-    <row r="21" spans="1:28" ht="160">
-      <c r="A21" s="11" t="s">
-        <v>96</v>
+    <row r="21" spans="1:28" ht="99.75">
+      <c r="A21" s="20" t="s">
+        <v>89</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="37" t="s">
-        <v>98</v>
+      <c r="E21" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="F21" s="12">
-        <v>44841</v>
+        <v>45025</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="K21" s="36">
-        <v>44293</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="K21" s="15"/>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
       <c r="N21" s="9"/>
@@ -2998,38 +3005,40 @@
       <c r="AA21" s="9"/>
       <c r="AB21" s="9"/>
     </row>
-    <row r="22" spans="1:28" ht="96">
-      <c r="A22" s="20" t="s">
-        <v>103</v>
+    <row r="22" spans="1:28" ht="142.5">
+      <c r="A22" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="35" t="s">
-        <v>106</v>
+      <c r="E22" s="37" t="s">
+        <v>98</v>
       </c>
       <c r="F22" s="12">
-        <v>45182</v>
+        <v>44841</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="K22" s="15"/>
+        <v>102</v>
+      </c>
+      <c r="K22" s="36">
+        <v>44293</v>
+      </c>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
       <c r="N22" s="9"/>
@@ -3048,33 +3057,37 @@
       <c r="AA22" s="9"/>
       <c r="AB22" s="9"/>
     </row>
-    <row r="23" spans="1:28" ht="124.5" customHeight="1">
-      <c r="A23" s="77" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="74" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="38" t="s">
+    <row r="23" spans="1:28" ht="85.5">
+      <c r="A23" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="39" t="s">
-        <v>114</v>
+      <c r="E23" s="35" t="s">
+        <v>106</v>
       </c>
       <c r="F23" s="12">
-        <v>44809</v>
-      </c>
-      <c r="G23" s="64" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23" s="68" t="s">
-        <v>116</v>
-      </c>
-      <c r="I23" s="69"/>
-      <c r="J23" s="70"/>
+        <v>45182</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="K23" s="15"/>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
@@ -3094,25 +3107,33 @@
       <c r="AA23" s="9"/>
       <c r="AB23" s="9"/>
     </row>
-    <row r="24" spans="1:28" ht="70.5" customHeight="1">
-      <c r="A24" s="65"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="10" t="s">
-        <v>14</v>
+    <row r="24" spans="1:28" ht="124.5" customHeight="1">
+      <c r="A24" s="76" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="40" t="s">
-        <v>117</v>
+      <c r="E24" s="39" t="s">
+        <v>114</v>
       </c>
       <c r="F24" s="12">
-        <v>45534</v>
-      </c>
-      <c r="G24" s="65"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="73"/>
+        <v>44809</v>
+      </c>
+      <c r="G24" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="H24" s="78" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="79"/>
+      <c r="J24" s="80"/>
       <c r="K24" s="15"/>
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
@@ -3132,36 +3153,26 @@
       <c r="AA24" s="9"/>
       <c r="AB24" s="9"/>
     </row>
-    <row r="25" spans="1:28" ht="217.5" customHeight="1">
-      <c r="A25" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="17" t="s">
+    <row r="25" spans="1:28" ht="70.5" customHeight="1">
+      <c r="A25" s="72"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="37" t="s">
-        <v>121</v>
+      <c r="E25" s="40" t="s">
+        <v>117</v>
       </c>
       <c r="F25" s="12">
-        <v>44839</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="62" t="s">
-        <v>123</v>
-      </c>
-      <c r="I25" s="63"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="15" t="s">
-        <v>31</v>
-      </c>
+        <v>45534</v>
+      </c>
+      <c r="G25" s="72"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="82"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="15"/>
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="9"/>
@@ -3180,125 +3191,123 @@
       <c r="AA25" s="9"/>
       <c r="AB25" s="9"/>
     </row>
-    <row r="26" spans="1:28" ht="267" customHeight="1">
-      <c r="A26" s="64" t="s">
+    <row r="26" spans="1:28" ht="217.5" customHeight="1">
+      <c r="A26" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="12">
+        <v>44839</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" s="69"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+    </row>
+    <row r="27" spans="1:28" ht="267" customHeight="1">
+      <c r="A27" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="B26" s="74" t="s">
+      <c r="B27" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="F26" s="12">
-        <v>45190</v>
-      </c>
-      <c r="G26" s="74" t="s">
-        <v>127</v>
-      </c>
-      <c r="H26" s="74" t="s">
-        <v>128</v>
-      </c>
-      <c r="I26" s="75" t="s">
-        <v>129</v>
-      </c>
-      <c r="J26" s="75" t="s">
-        <v>128</v>
-      </c>
-      <c r="K26" s="41"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-      <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="2"/>
-    </row>
-    <row r="27" spans="1:28" ht="48">
-      <c r="A27" s="65"/>
-      <c r="B27" s="65"/>
       <c r="C27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="37" t="s">
-        <v>130</v>
+      <c r="E27" s="35" t="s">
+        <v>126</v>
       </c>
       <c r="F27" s="12">
-        <v>45400</v>
-      </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-    </row>
-    <row r="28" spans="1:28" ht="272">
-      <c r="A28" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>132</v>
-      </c>
+        <v>45190</v>
+      </c>
+      <c r="G27" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="84" t="s">
+        <v>129</v>
+      </c>
+      <c r="J27" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="41"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2"/>
+    </row>
+    <row r="28" spans="1:28" ht="42.75">
+      <c r="A28" s="72"/>
+      <c r="B28" s="72"/>
       <c r="C28" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="43" t="s">
+      <c r="D28" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="F28" s="45">
-        <v>45286</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>136</v>
-      </c>
+      <c r="E28" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="F28" s="12">
+        <v>45400</v>
+      </c>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
       <c r="K28" s="15"/>
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
@@ -3318,40 +3327,38 @@
       <c r="AA28" s="9"/>
       <c r="AB28" s="9"/>
     </row>
-    <row r="29" spans="1:28" ht="144">
+    <row r="29" spans="1:28" ht="242.25">
       <c r="A29" s="20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="F29" s="12">
-        <v>45489</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="K29" s="46">
-        <v>44566</v>
-      </c>
+      <c r="E29" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="45">
+        <v>45286</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="K29" s="15"/>
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
       <c r="N29" s="9"/>
@@ -3370,38 +3377,40 @@
       <c r="AA29" s="9"/>
       <c r="AB29" s="9"/>
     </row>
-    <row r="30" spans="1:28" ht="96">
+    <row r="30" spans="1:28" ht="128.25">
       <c r="A30" s="20" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>145</v>
+        <v>137</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>138</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F30" s="12">
-        <v>45303</v>
+        <v>45489</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="K30" s="15"/>
+        <v>143</v>
+      </c>
+      <c r="K30" s="46">
+        <v>44566</v>
+      </c>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" s="9"/>
@@ -3420,36 +3429,36 @@
       <c r="AA30" s="9"/>
       <c r="AB30" s="9"/>
     </row>
-    <row r="31" spans="1:28" ht="64">
+    <row r="31" spans="1:28" ht="85.5">
       <c r="A31" s="20" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="11" t="s">
-        <v>153</v>
+      <c r="E31" s="37" t="s">
+        <v>146</v>
       </c>
       <c r="F31" s="12">
-        <v>45416</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>157</v>
+        <v>45303</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>150</v>
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="16"/>
@@ -3470,36 +3479,36 @@
       <c r="AA31" s="9"/>
       <c r="AB31" s="9"/>
     </row>
-    <row r="32" spans="1:28" ht="138" customHeight="1">
-      <c r="A32" s="32" t="s">
-        <v>158</v>
+    <row r="32" spans="1:28" ht="71.25">
+      <c r="A32" s="20" t="s">
+        <v>151</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F32" s="12">
-        <v>45586</v>
+        <v>45416</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="I32" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="J32" s="32" t="s">
-        <v>163</v>
+        <v>155</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>157</v>
       </c>
       <c r="K32" s="15"/>
       <c r="L32" s="16"/>
@@ -3520,30 +3529,36 @@
       <c r="AA32" s="9"/>
       <c r="AB32" s="9"/>
     </row>
-    <row r="33" spans="1:28" ht="112">
-      <c r="A33" s="20" t="s">
-        <v>164</v>
+    <row r="33" spans="1:28" ht="138" customHeight="1">
+      <c r="A33" s="32" t="s">
+        <v>158</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="C33" s="10"/>
+        <v>159</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="D33" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" s="12">
+        <v>45586</v>
+      </c>
       <c r="G33" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>170</v>
+        <v>161</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I33" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="J33" s="32" t="s">
+        <v>163</v>
       </c>
       <c r="K33" s="15"/>
       <c r="L33" s="16"/>
@@ -3564,30 +3579,30 @@
       <c r="AA33" s="9"/>
       <c r="AB33" s="9"/>
     </row>
-    <row r="34" spans="1:28" ht="144">
-      <c r="A34" s="11" t="s">
-        <v>171</v>
+    <row r="34" spans="1:28" ht="99.75">
+      <c r="A34" s="20" t="s">
+        <v>164</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C34" s="10"/>
-      <c r="D34" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E34" s="10"/>
+      <c r="D34" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="E34" s="17"/>
       <c r="F34" s="12"/>
       <c r="G34" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>175</v>
+        <v>167</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>168</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="K34" s="15"/>
       <c r="L34" s="16"/>
@@ -3608,12 +3623,12 @@
       <c r="AA34" s="9"/>
       <c r="AB34" s="9"/>
     </row>
-    <row r="35" spans="1:28" ht="112">
-      <c r="A35" s="32" t="s">
-        <v>178</v>
+    <row r="35" spans="1:28" ht="142.5">
+      <c r="A35" s="11" t="s">
+        <v>171</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10" t="s">
@@ -3622,16 +3637,16 @@
       <c r="E35" s="10"/>
       <c r="F35" s="12"/>
       <c r="G35" s="13" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="16"/>
@@ -3652,12 +3667,12 @@
       <c r="AA35" s="9"/>
       <c r="AB35" s="9"/>
     </row>
-    <row r="36" spans="1:28" ht="153.75" customHeight="1">
-      <c r="A36" s="11" t="s">
-        <v>184</v>
+    <row r="36" spans="1:28" ht="99.75">
+      <c r="A36" s="32" t="s">
+        <v>178</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10" t="s">
@@ -3666,16 +3681,16 @@
       <c r="E36" s="10"/>
       <c r="F36" s="12"/>
       <c r="G36" s="13" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>181</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="K36" s="15"/>
       <c r="L36" s="16"/>
@@ -3696,12 +3711,12 @@
       <c r="AA36" s="9"/>
       <c r="AB36" s="9"/>
     </row>
-    <row r="37" spans="1:28" ht="160">
-      <c r="A37" s="47" t="s">
-        <v>189</v>
+    <row r="37" spans="1:28" ht="153.75" customHeight="1">
+      <c r="A37" s="11" t="s">
+        <v>184</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10" t="s">
@@ -3710,16 +3725,16 @@
       <c r="E37" s="10"/>
       <c r="F37" s="12"/>
       <c r="G37" s="13" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>194</v>
+        <v>187</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>188</v>
       </c>
       <c r="K37" s="15"/>
       <c r="L37" s="16"/>
@@ -3740,12 +3755,12 @@
       <c r="AA37" s="9"/>
       <c r="AB37" s="9"/>
     </row>
-    <row r="38" spans="1:28" ht="80">
-      <c r="A38" s="20" t="s">
-        <v>195</v>
+    <row r="38" spans="1:28" ht="142.5">
+      <c r="A38" s="47" t="s">
+        <v>189</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10" t="s">
@@ -3754,16 +3769,16 @@
       <c r="E38" s="10"/>
       <c r="F38" s="12"/>
       <c r="G38" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H38" s="22" t="s">
-        <v>198</v>
+        <v>191</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>70</v>
+        <v>193</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>194</v>
       </c>
       <c r="K38" s="15"/>
       <c r="L38" s="16"/>
@@ -3784,12 +3799,12 @@
       <c r="AA38" s="9"/>
       <c r="AB38" s="9"/>
     </row>
-    <row r="39" spans="1:28" ht="64">
-      <c r="A39" s="48" t="s">
-        <v>200</v>
+    <row r="39" spans="1:28" ht="71.25">
+      <c r="A39" s="20" t="s">
+        <v>195</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10" t="s">
@@ -3798,16 +3813,16 @@
       <c r="E39" s="10"/>
       <c r="F39" s="12"/>
       <c r="G39" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>203</v>
+        <v>197</v>
+      </c>
+      <c r="H39" s="22" t="s">
+        <v>198</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>205</v>
+        <v>70</v>
       </c>
       <c r="K39" s="15"/>
       <c r="L39" s="16"/>
@@ -3828,12 +3843,12 @@
       <c r="AA39" s="9"/>
       <c r="AB39" s="9"/>
     </row>
-    <row r="40" spans="1:28" ht="208">
-      <c r="A40" s="20" t="s">
-        <v>206</v>
+    <row r="40" spans="1:28" ht="57">
+      <c r="A40" s="48" t="s">
+        <v>200</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
@@ -3841,17 +3856,17 @@
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="12"/>
-      <c r="G40" s="49" t="s">
-        <v>207</v>
+      <c r="G40" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="K40" s="15"/>
       <c r="L40" s="16"/>
@@ -3872,12 +3887,12 @@
       <c r="AA40" s="9"/>
       <c r="AB40" s="9"/>
     </row>
-    <row r="41" spans="1:28" ht="96">
+    <row r="41" spans="1:28" ht="199.5">
       <c r="A41" s="20" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
@@ -3885,17 +3900,17 @@
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="12"/>
-      <c r="G41" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>214</v>
+      <c r="G41" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>210</v>
       </c>
       <c r="K41" s="15"/>
       <c r="L41" s="16"/>
@@ -3916,12 +3931,12 @@
       <c r="AA41" s="9"/>
       <c r="AB41" s="9"/>
     </row>
-    <row r="42" spans="1:28" ht="128">
+    <row r="42" spans="1:28" ht="85.5">
       <c r="A42" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10" t="s">
@@ -3930,16 +3945,16 @@
       <c r="E42" s="10"/>
       <c r="F42" s="12"/>
       <c r="G42" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="I42" s="50" t="s">
-        <v>218</v>
+        <v>141</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>213</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="K42" s="15"/>
       <c r="L42" s="16"/>
@@ -3960,34 +3975,30 @@
       <c r="AA42" s="9"/>
       <c r="AB42" s="9"/>
     </row>
-    <row r="43" spans="1:28" ht="176">
+    <row r="43" spans="1:28" ht="114">
       <c r="A43" s="20" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>221</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C43" s="10"/>
       <c r="D43" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>223</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="E43" s="10"/>
       <c r="F43" s="12"/>
       <c r="G43" s="10" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>226</v>
+        <v>217</v>
+      </c>
+      <c r="I43" s="50" t="s">
+        <v>218</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="K43" s="15"/>
       <c r="L43" s="16"/>
@@ -4008,30 +4019,34 @@
       <c r="AA43" s="9"/>
       <c r="AB43" s="9"/>
     </row>
-    <row r="44" spans="1:28" ht="144">
-      <c r="A44" s="10" t="s">
-        <v>227</v>
+    <row r="44" spans="1:28" ht="156.75">
+      <c r="A44" s="20" t="s">
+        <v>220</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C44" s="10"/>
+        <v>220</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>221</v>
+      </c>
       <c r="D44" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E44" s="10"/>
+        <v>222</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="F44" s="12"/>
       <c r="G44" s="10" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="16"/>
@@ -4052,12 +4067,12 @@
       <c r="AA44" s="9"/>
       <c r="AB44" s="9"/>
     </row>
-    <row r="45" spans="1:28" ht="128">
-      <c r="A45" s="20" t="s">
-        <v>233</v>
+    <row r="45" spans="1:28" ht="142.5">
+      <c r="A45" s="10" t="s">
+        <v>227</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10" t="s">
@@ -4066,16 +4081,16 @@
       <c r="E45" s="10"/>
       <c r="F45" s="12"/>
       <c r="G45" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="16"/>
@@ -4096,30 +4111,30 @@
       <c r="AA45" s="9"/>
       <c r="AB45" s="9"/>
     </row>
-    <row r="46" spans="1:28" ht="128">
-      <c r="A46" s="13" t="s">
-        <v>238</v>
+    <row r="46" spans="1:28" ht="114">
+      <c r="A46" s="20" t="s">
+        <v>233</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C46" s="10"/>
-      <c r="D46" s="51" t="s">
+      <c r="D46" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="E46" s="52"/>
+      <c r="E46" s="10"/>
       <c r="F46" s="12"/>
-      <c r="G46" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>243</v>
+      <c r="G46" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="16"/>
@@ -4140,12 +4155,12 @@
       <c r="AA46" s="9"/>
       <c r="AB46" s="9"/>
     </row>
-    <row r="47" spans="1:28" ht="112">
+    <row r="47" spans="1:28" ht="114">
       <c r="A47" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>245</v>
+        <v>238</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>239</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="51" t="s">
@@ -4154,16 +4169,16 @@
       <c r="E47" s="52"/>
       <c r="F47" s="12"/>
       <c r="G47" s="13" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="K47" s="15"/>
       <c r="L47" s="16"/>
@@ -4184,12 +4199,12 @@
       <c r="AA47" s="9"/>
       <c r="AB47" s="9"/>
     </row>
-    <row r="48" spans="1:28" ht="95.25" customHeight="1">
+    <row r="48" spans="1:28" ht="114">
       <c r="A48" s="13" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="51" t="s">
@@ -4198,16 +4213,16 @@
       <c r="E48" s="52"/>
       <c r="F48" s="12"/>
       <c r="G48" s="13" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="K48" s="15"/>
       <c r="L48" s="16"/>
@@ -4228,32 +4243,30 @@
       <c r="AA48" s="9"/>
       <c r="AB48" s="9"/>
     </row>
-    <row r="49" spans="1:28" ht="64">
-      <c r="A49" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>257</v>
+    <row r="49" spans="1:28" ht="95.25" customHeight="1">
+      <c r="A49" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>251</v>
       </c>
       <c r="C49" s="10"/>
-      <c r="D49" s="53" t="s">
-        <v>258</v>
-      </c>
-      <c r="E49" s="53" t="s">
-        <v>14</v>
-      </c>
+      <c r="D49" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" s="52"/>
       <c r="F49" s="12"/>
       <c r="G49" s="13" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="K49" s="15"/>
       <c r="L49" s="16"/>
@@ -4274,12 +4287,12 @@
       <c r="AA49" s="9"/>
       <c r="AB49" s="9"/>
     </row>
-    <row r="50" spans="1:28" ht="144">
+    <row r="50" spans="1:28" ht="57">
       <c r="A50" s="20" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="53" t="s">
@@ -4290,16 +4303,16 @@
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="13" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="K50" s="15"/>
       <c r="L50" s="16"/>
@@ -4320,12 +4333,12 @@
       <c r="AA50" s="9"/>
       <c r="AB50" s="9"/>
     </row>
-    <row r="51" spans="1:28" ht="80">
+    <row r="51" spans="1:28" ht="156.75">
       <c r="A51" s="20" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="53" t="s">
@@ -4336,20 +4349,18 @@
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="13" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="K51" s="54">
-        <v>44213</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="K51" s="15"/>
       <c r="L51" s="16"/>
       <c r="M51" s="16"/>
       <c r="N51" s="9"/>
@@ -4368,12 +4379,12 @@
       <c r="AA51" s="9"/>
       <c r="AB51" s="9"/>
     </row>
-    <row r="52" spans="1:28" ht="96.75" customHeight="1">
+    <row r="52" spans="1:28" ht="71.25">
       <c r="A52" s="20" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="53" t="s">
@@ -4384,18 +4395,20 @@
       </c>
       <c r="F52" s="12"/>
       <c r="G52" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>278</v>
+        <v>271</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>272</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="K52" s="15"/>
+        <v>274</v>
+      </c>
+      <c r="K52" s="54">
+        <v>44213</v>
+      </c>
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
       <c r="N52" s="9"/>
@@ -4414,33 +4427,35 @@
       <c r="AA52" s="9"/>
       <c r="AB52" s="9"/>
     </row>
-    <row r="53" spans="1:28" ht="180" customHeight="1">
+    <row r="53" spans="1:28" ht="96.75" customHeight="1">
       <c r="A53" s="20" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="53" t="s">
         <v>258</v>
       </c>
       <c r="E53" s="53" t="s">
-        <v>283</v>
+        <v>14</v>
       </c>
       <c r="F53" s="12"/>
       <c r="G53" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="H53" s="62" t="s">
-        <v>285</v>
-      </c>
-      <c r="I53" s="63"/>
+        <v>277</v>
+      </c>
+      <c r="H53" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>279</v>
+      </c>
       <c r="J53" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="K53" s="25"/>
-      <c r="L53" s="15"/>
+        <v>280</v>
+      </c>
+      <c r="K53" s="15"/>
+      <c r="L53" s="16"/>
       <c r="M53" s="16"/>
       <c r="N53" s="9"/>
       <c r="O53" s="9"/>
@@ -4458,19 +4473,33 @@
       <c r="AA53" s="9"/>
       <c r="AB53" s="9"/>
     </row>
-    <row r="54" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A54" s="14"/>
-      <c r="B54" s="10"/>
+    <row r="54" spans="1:28" ht="180" customHeight="1">
+      <c r="A54" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>282</v>
+      </c>
       <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="16"/>
+      <c r="D54" s="53" t="s">
+        <v>258</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="H54" s="77" t="s">
+        <v>285</v>
+      </c>
+      <c r="I54" s="69"/>
+      <c r="J54" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="K54" s="25"/>
+      <c r="L54" s="15"/>
       <c r="M54" s="16"/>
       <c r="N54" s="9"/>
       <c r="O54" s="9"/>
@@ -4519,19 +4548,19 @@
       <c r="AB55" s="9"/>
     </row>
     <row r="56" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A56" s="55"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="58"/>
-      <c r="H56" s="58"/>
-      <c r="I56" s="58"/>
-      <c r="J56" s="58"/>
-      <c r="K56" s="59"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
+      <c r="A56" s="14"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
       <c r="N56" s="9"/>
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
@@ -4549,7 +4578,7 @@
       <c r="AB56" s="9"/>
     </row>
     <row r="57" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A57" s="60"/>
+      <c r="A57" s="55"/>
       <c r="B57" s="56"/>
       <c r="C57" s="56"/>
       <c r="D57" s="56"/>
@@ -4644,7 +4673,7 @@
       <c r="C60" s="56"/>
       <c r="D60" s="56"/>
       <c r="E60" s="56"/>
-      <c r="F60" s="61"/>
+      <c r="F60" s="57"/>
       <c r="G60" s="58"/>
       <c r="H60" s="58"/>
       <c r="I60" s="58"/>
@@ -9559,7 +9588,7 @@
       <c r="AB223" s="9"/>
     </row>
     <row r="224" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A224" s="9"/>
+      <c r="A224" s="60"/>
       <c r="B224" s="56"/>
       <c r="C224" s="56"/>
       <c r="D224" s="56"/>
@@ -32958,8 +32987,60 @@
       <c r="AA1003" s="9"/>
       <c r="AB1003" s="9"/>
     </row>
+    <row r="1004" spans="1:28" ht="15.75" customHeight="1">
+      <c r="A1004" s="9"/>
+      <c r="B1004" s="56"/>
+      <c r="C1004" s="56"/>
+      <c r="D1004" s="56"/>
+      <c r="E1004" s="56"/>
+      <c r="F1004" s="61"/>
+      <c r="G1004" s="58"/>
+      <c r="H1004" s="58"/>
+      <c r="I1004" s="58"/>
+      <c r="J1004" s="58"/>
+      <c r="K1004" s="59"/>
+      <c r="L1004" s="9"/>
+      <c r="M1004" s="9"/>
+      <c r="N1004" s="9"/>
+      <c r="O1004" s="9"/>
+      <c r="P1004" s="9"/>
+      <c r="Q1004" s="9"/>
+      <c r="R1004" s="9"/>
+      <c r="S1004" s="9"/>
+      <c r="T1004" s="9"/>
+      <c r="U1004" s="9"/>
+      <c r="V1004" s="9"/>
+      <c r="W1004" s="9"/>
+      <c r="X1004" s="9"/>
+      <c r="Y1004" s="9"/>
+      <c r="Z1004" s="9"/>
+      <c r="AA1004" s="9"/>
+      <c r="AB1004" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="H24:J25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="H5:I5"/>
@@ -32967,31 +33048,9 @@
     <mergeCell ref="G7:G10"/>
     <mergeCell ref="H7:H10"/>
     <mergeCell ref="I7:I10"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="H23:J24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D55" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D16:D56 D4:D15" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Published,Awaiting publication,Analysis underway,Analysis completed,On hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -33014,63 +33073,63 @@
     <hyperlink ref="C13" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="E13" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="E14" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="A15" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C15" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="E15" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A16" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="E16" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="E17" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="E18" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A19" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="E19" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="A20" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="E20" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="A21" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="E21" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="A22" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C22" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="E22" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="A23" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C23" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="E23" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="E24" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="A25" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C25" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="E25" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="E26" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="E27" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="A28" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="E28" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="A29" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C29" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="E29" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="A30" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C30" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="E30" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="A31" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="E31" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="A32" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="E32" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="I32" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="J32" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="A33" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="A34" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="A35" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="A36" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="A37" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="A38" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="A39" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="A40" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="A41" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="A42" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="A43" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C43" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="A45" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="A49" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="A50" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="A51" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="A52" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="A53" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="A16" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C16" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="E16" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A17" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="E17" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="E18" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="E19" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="A20" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="E20" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="A21" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="E21" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="A22" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="E22" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="A23" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C23" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="E23" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="A24" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C24" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="E24" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="E25" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="A26" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C26" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="E26" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="E27" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="E28" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="A29" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="E29" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="A30" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C30" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="E30" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="A31" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C31" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="E31" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="A32" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="E32" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="A33" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="E33" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="I33" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="J33" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="A34" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="A35" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="A36" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="A37" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="A38" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="A39" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="A40" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="A41" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="A42" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="A43" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="A44" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C44" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="A46" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="A50" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="A51" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="A52" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="A53" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="A54" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -33080,26 +33139,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F3AB5A6-7DB8-2D45-B511-7E2440E2213F}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="43.83203125" customWidth="1"/>
+    <col min="1" max="1" width="21.796875" customWidth="1"/>
+    <col min="2" max="2" width="43.796875" customWidth="1"/>
     <col min="3" max="3" width="45.6640625" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="85" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-    </row>
-    <row r="2" spans="1:5" ht="16" thickBot="1"/>
-    <row r="3" spans="1:5" ht="17" thickTop="1">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+    </row>
+    <row r="2" spans="1:5" ht="14.65" thickBot="1"/>
+    <row r="3" spans="1:5" ht="14.65" thickTop="1">
       <c r="A3" s="3" t="s">
         <v>289</v>
       </c>
@@ -33117,19 +33176,19 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="63" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="63" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="63" t="s">
         <v>297</v>
       </c>
-      <c r="E4" s="83" t="s">
+      <c r="E4" s="64" t="s">
         <v>298</v>
       </c>
     </row>

--- a/Analyses/Partner-Analyses-Metadata.xlsx
+++ b/Analyses/Partner-Analyses-Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/otss1968_ox_ac_uk/Documents/Documents/GitHub/CCP/Analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DAD1587-EC9D-45A5-9398-A39260F98FDC}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Partner Analyses" sheetId="1" r:id="rId1"/>
     <sheet name="Sub-processors" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partner Analyses'!$A$3:$Z$56</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="314">
   <si>
     <t>ISARIC Partner Analyses</t>
   </si>
@@ -1151,6 +1154,9 @@
   <si>
     <t>Omicron surge impact on acute kidney injury in ICU patients: A study using the ISARIC COVID-19 database | PLOS One</t>
   </si>
+  <si>
+    <t>Immune dysregulation through longitudinal lymphocyte trajectories and their clinical determinants in hospitalized COVID-19 patients</t>
+  </si>
 </sst>
 </file>
 
@@ -1626,7 +1632,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1810,66 +1816,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1881,6 +1832,64 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2117,18 +2126,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -2146,17 +2155,17 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
+    <row r="2" spans="1:26" ht="14.65" thickBot="1">
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -2174,7 +2183,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="28.5">
+    <row r="3" spans="1:26" ht="28.9" thickTop="1">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2246,10 +2255,10 @@
       <c r="G4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="84" t="s">
+      <c r="H4" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="66"/>
+      <c r="I4" s="76"/>
       <c r="J4" s="14" t="s">
         <v>18</v>
       </c>
@@ -2292,10 +2301,10 @@
       <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="84" t="s">
+      <c r="H5" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="66"/>
+      <c r="I5" s="76"/>
       <c r="J5" s="14" t="s">
         <v>18</v>
       </c>
@@ -2369,7 +2378,7 @@
       <c r="Z6" s="9"/>
     </row>
     <row r="7" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="82" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="77" t="s">
@@ -2387,13 +2396,13 @@
       <c r="F7" s="12">
         <v>44540</v>
       </c>
-      <c r="G7" s="67" t="s">
+      <c r="G7" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="69" t="s">
+      <c r="H7" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="69" t="s">
+      <c r="I7" s="81" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="19" t="s">
@@ -2417,8 +2426,8 @@
       <c r="Z7" s="9"/>
     </row>
     <row r="8" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A8" s="70"/>
-      <c r="B8" s="70"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="78"/>
       <c r="C8" s="58" t="s">
         <v>13</v>
       </c>
@@ -2431,9 +2440,9 @@
       <c r="F8" s="12">
         <v>44772</v>
       </c>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="78"/>
       <c r="J8" s="19" t="s">
         <v>39</v>
       </c>
@@ -2455,8 +2464,8 @@
       <c r="Z8" s="9"/>
     </row>
     <row r="9" spans="1:26" ht="39.75" customHeight="1">
-      <c r="A9" s="70"/>
-      <c r="B9" s="70"/>
+      <c r="A9" s="78"/>
+      <c r="B9" s="78"/>
       <c r="C9" s="58" t="s">
         <v>13</v>
       </c>
@@ -2469,9 +2478,9 @@
       <c r="F9" s="12">
         <v>44817</v>
       </c>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
       <c r="J9" s="19" t="s">
         <v>39</v>
       </c>
@@ -2493,8 +2502,8 @@
       <c r="Z9" s="9"/>
     </row>
     <row r="10" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A10" s="68"/>
-      <c r="B10" s="68"/>
+      <c r="A10" s="79"/>
+      <c r="B10" s="79"/>
       <c r="C10" s="58" t="s">
         <v>13</v>
       </c>
@@ -2507,9 +2516,9 @@
       <c r="F10" s="12">
         <v>45055</v>
       </c>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
       <c r="J10" s="19" t="s">
         <v>39</v>
       </c>
@@ -2631,7 +2640,7 @@
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="82" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="77" t="s">
@@ -2649,16 +2658,16 @@
       <c r="F13" s="12">
         <v>44671</v>
       </c>
-      <c r="G13" s="67" t="s">
+      <c r="G13" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="67" t="s">
+      <c r="H13" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="67" t="s">
+      <c r="I13" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="69" t="s">
+      <c r="J13" s="81" t="s">
         <v>62</v>
       </c>
       <c r="K13" s="28">
@@ -2681,8 +2690,8 @@
       <c r="Z13" s="9"/>
     </row>
     <row r="14" spans="1:26" s="56" customFormat="1" ht="66.75" customHeight="1">
-      <c r="A14" s="89"/>
-      <c r="B14" s="90"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="58" t="s">
         <v>13</v>
       </c>
@@ -2695,10 +2704,10 @@
       <c r="F14" s="12">
         <v>45072</v>
       </c>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="92"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="88"/>
       <c r="K14" s="28"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
@@ -2717,24 +2726,24 @@
       <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="78.75" customHeight="1">
-      <c r="A15" s="68"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="93" t="s">
+      <c r="A15" s="79"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="94" t="s">
+      <c r="D15" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="95" t="s">
+      <c r="E15" s="70" t="s">
         <v>312</v>
       </c>
-      <c r="F15" s="96">
+      <c r="F15" s="71">
         <v>45981</v>
       </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
       <c r="K15" s="28"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -2803,7 +2812,7 @@
       <c r="Z16" s="9"/>
     </row>
     <row r="17" spans="1:26" ht="45" customHeight="1">
-      <c r="A17" s="79" t="s">
+      <c r="A17" s="82" t="s">
         <v>70</v>
       </c>
       <c r="B17" s="77" t="s">
@@ -2821,7 +2830,7 @@
       <c r="F17" s="12">
         <v>44814</v>
       </c>
-      <c r="G17" s="67" t="s">
+      <c r="G17" s="80" t="s">
         <v>73</v>
       </c>
       <c r="H17" s="21" t="s">
@@ -2853,8 +2862,8 @@
       <c r="Z17" s="9"/>
     </row>
     <row r="18" spans="1:26" ht="102" customHeight="1">
-      <c r="A18" s="70"/>
-      <c r="B18" s="70"/>
+      <c r="A18" s="78"/>
+      <c r="B18" s="78"/>
       <c r="C18" s="58" t="s">
         <v>13</v>
       </c>
@@ -2867,7 +2876,7 @@
       <c r="F18" s="12">
         <v>45331</v>
       </c>
-      <c r="G18" s="70"/>
+      <c r="G18" s="78"/>
       <c r="H18" s="21" t="s">
         <v>74</v>
       </c>
@@ -2895,8 +2904,8 @@
       <c r="Z18" s="9"/>
     </row>
     <row r="19" spans="1:26" ht="78" customHeight="1">
-      <c r="A19" s="70"/>
-      <c r="B19" s="68"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="79"/>
       <c r="C19" s="58" t="s">
         <v>13</v>
       </c>
@@ -2909,7 +2918,7 @@
       <c r="F19" s="12">
         <v>45266</v>
       </c>
-      <c r="G19" s="70"/>
+      <c r="G19" s="78"/>
       <c r="H19" s="21" t="s">
         <v>79</v>
       </c>
@@ -3131,7 +3140,7 @@
       <c r="Z23" s="9"/>
     </row>
     <row r="24" spans="1:26" ht="124.5" customHeight="1">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="85" t="s">
         <v>110</v>
       </c>
       <c r="B24" s="77" t="s">
@@ -3149,14 +3158,14 @@
       <c r="F24" s="12">
         <v>44809</v>
       </c>
-      <c r="G24" s="67" t="s">
+      <c r="G24" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="71" t="s">
+      <c r="H24" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="I24" s="72"/>
-      <c r="J24" s="73"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="91"/>
       <c r="K24" s="15"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
@@ -3175,8 +3184,8 @@
       <c r="Z24" s="9"/>
     </row>
     <row r="25" spans="1:26" ht="70.5" customHeight="1">
-      <c r="A25" s="68"/>
-      <c r="B25" s="68"/>
+      <c r="A25" s="79"/>
+      <c r="B25" s="79"/>
       <c r="C25" s="58" t="s">
         <v>13</v>
       </c>
@@ -3189,10 +3198,10 @@
       <c r="F25" s="12">
         <v>45534</v>
       </c>
-      <c r="G25" s="68"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="76"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="94"/>
       <c r="K25" s="15"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
@@ -3232,10 +3241,10 @@
       <c r="G26" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="65" t="s">
+      <c r="H26" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="I26" s="66"/>
+      <c r="I26" s="76"/>
       <c r="J26" s="14"/>
       <c r="K26" s="15" t="s">
         <v>30</v>
@@ -3257,7 +3266,7 @@
       <c r="Z26" s="9"/>
     </row>
     <row r="27" spans="1:26" ht="267" customHeight="1">
-      <c r="A27" s="79" t="s">
+      <c r="A27" s="82" t="s">
         <v>123</v>
       </c>
       <c r="B27" s="77" t="s">
@@ -3281,10 +3290,10 @@
       <c r="H27" s="77" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="78" t="s">
+      <c r="I27" s="95" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="78" t="s">
+      <c r="J27" s="95" t="s">
         <v>127</v>
       </c>
       <c r="K27" s="35"/>
@@ -3305,8 +3314,8 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="42.75">
-      <c r="A28" s="68"/>
-      <c r="B28" s="68"/>
+      <c r="A28" s="79"/>
+      <c r="B28" s="79"/>
       <c r="C28" s="58" t="s">
         <v>13</v>
       </c>
@@ -3319,10 +3328,10 @@
       <c r="F28" s="12">
         <v>45400</v>
       </c>
-      <c r="G28" s="68"/>
-      <c r="H28" s="68"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="68"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
       <c r="K28" s="15"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
@@ -3717,9 +3726,11 @@
       </c>
       <c r="C37" s="58"/>
       <c r="D37" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="E37" s="97" t="s">
+        <v>313</v>
+      </c>
       <c r="F37" s="12"/>
       <c r="G37" s="13" t="s">
         <v>187</v>
@@ -4536,10 +4547,10 @@
       <c r="G56" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="H56" s="65" t="s">
+      <c r="H56" s="86" t="s">
         <v>299</v>
       </c>
-      <c r="I56" s="66"/>
+      <c r="I56" s="76"/>
       <c r="J56" s="13" t="s">
         <v>300</v>
       </c>
@@ -31106,22 +31117,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="I7:I10"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
     <mergeCell ref="H56:I56"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="H13:H15"/>
@@ -31135,6 +31130,22 @@
     <mergeCell ref="H27:H28"/>
     <mergeCell ref="I27:I28"/>
     <mergeCell ref="J27:J28"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D56" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -31241,13 +31252,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="96" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
       <c r="A2" s="56"/>
@@ -31256,37 +31267,37 @@
       <c r="D2" s="56"/>
       <c r="E2" s="56"/>
     </row>
-    <row r="3" spans="1:5" ht="28.9" thickTop="1">
-      <c r="A3" s="86" t="s">
+    <row r="3" spans="1:5" ht="14.65" thickTop="1">
+      <c r="A3" s="65" t="s">
         <v>302</v>
       </c>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="65" t="s">
         <v>303</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="65" t="s">
         <v>304</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E3" s="86" t="s">
+      <c r="E3" s="65" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="66" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="66" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="87" t="s">
+      <c r="C4" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="D4" s="87" t="s">
+      <c r="D4" s="66" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="88" t="s">
+      <c r="E4" s="67" t="s">
         <v>311</v>
       </c>
     </row>

--- a/Analyses/Partner-Analyses-Metadata.xlsx
+++ b/Analyses/Partner-Analyses-Metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/otss1968_ox_ac_uk/Documents/Documents/GitHub/CCP/Analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DAD1587-EC9D-45A5-9398-A39260F98FDC}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A05085-C896-4B7B-B1F1-F5B514CAA1E5}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Partner Analyses" sheetId="1" r:id="rId1"/>
@@ -1833,24 +1833,36 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1865,30 +1877,18 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2126,18 +2126,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -2156,16 +2156,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="14.65" thickBot="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -2255,10 +2255,10 @@
       <c r="G4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="75" t="s">
+      <c r="H4" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="76"/>
+      <c r="I4" s="73"/>
       <c r="J4" s="14" t="s">
         <v>18</v>
       </c>
@@ -2301,10 +2301,10 @@
       <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="75" t="s">
+      <c r="H5" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="76"/>
+      <c r="I5" s="73"/>
       <c r="J5" s="14" t="s">
         <v>18</v>
       </c>
@@ -2378,10 +2378,10 @@
       <c r="Z6" s="9"/>
     </row>
     <row r="7" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="86" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="58" t="s">
@@ -2396,13 +2396,13 @@
       <c r="F7" s="12">
         <v>44540</v>
       </c>
-      <c r="G7" s="80" t="s">
+      <c r="G7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="81" t="s">
+      <c r="H7" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="81" t="s">
+      <c r="I7" s="77" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="19" t="s">
@@ -2426,8 +2426,8 @@
       <c r="Z7" s="9"/>
     </row>
     <row r="8" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A8" s="78"/>
-      <c r="B8" s="78"/>
+      <c r="A8" s="79"/>
+      <c r="B8" s="79"/>
       <c r="C8" s="58" t="s">
         <v>13</v>
       </c>
@@ -2440,9 +2440,9 @@
       <c r="F8" s="12">
         <v>44772</v>
       </c>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="78"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79"/>
       <c r="J8" s="19" t="s">
         <v>39</v>
       </c>
@@ -2464,8 +2464,8 @@
       <c r="Z8" s="9"/>
     </row>
     <row r="9" spans="1:26" ht="39.75" customHeight="1">
-      <c r="A9" s="78"/>
-      <c r="B9" s="78"/>
+      <c r="A9" s="79"/>
+      <c r="B9" s="79"/>
       <c r="C9" s="58" t="s">
         <v>13</v>
       </c>
@@ -2478,9 +2478,9 @@
       <c r="F9" s="12">
         <v>44817</v>
       </c>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
       <c r="J9" s="19" t="s">
         <v>39</v>
       </c>
@@ -2502,8 +2502,8 @@
       <c r="Z9" s="9"/>
     </row>
     <row r="10" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A10" s="79"/>
-      <c r="B10" s="79"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="58" t="s">
         <v>13</v>
       </c>
@@ -2516,9 +2516,9 @@
       <c r="F10" s="12">
         <v>45055</v>
       </c>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
       <c r="J10" s="19" t="s">
         <v>39</v>
       </c>
@@ -2640,10 +2640,10 @@
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="86" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="60" t="s">
@@ -2658,16 +2658,16 @@
       <c r="F13" s="12">
         <v>44671</v>
       </c>
-      <c r="G13" s="80" t="s">
+      <c r="G13" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="80" t="s">
+      <c r="H13" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="80" t="s">
+      <c r="I13" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="81" t="s">
+      <c r="J13" s="77" t="s">
         <v>62</v>
       </c>
       <c r="K13" s="28">
@@ -2690,8 +2690,8 @@
       <c r="Z13" s="9"/>
     </row>
     <row r="14" spans="1:26" s="56" customFormat="1" ht="66.75" customHeight="1">
-      <c r="A14" s="83"/>
-      <c r="B14" s="84"/>
+      <c r="A14" s="89"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="58" t="s">
         <v>13</v>
       </c>
@@ -2704,10 +2704,10 @@
       <c r="F14" s="12">
         <v>45072</v>
       </c>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="88"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="78"/>
       <c r="K14" s="28"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
@@ -2726,8 +2726,8 @@
       <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="78.75" customHeight="1">
-      <c r="A15" s="79"/>
-      <c r="B15" s="79"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="76"/>
       <c r="C15" s="68" t="s">
         <v>13</v>
       </c>
@@ -2740,10 +2740,10 @@
       <c r="F15" s="71">
         <v>45981</v>
       </c>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
       <c r="K15" s="28"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -2812,10 +2812,10 @@
       <c r="Z16" s="9"/>
     </row>
     <row r="17" spans="1:26" ht="45" customHeight="1">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="77" t="s">
+      <c r="B17" s="86" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="58" t="s">
@@ -2830,7 +2830,7 @@
       <c r="F17" s="12">
         <v>44814</v>
       </c>
-      <c r="G17" s="80" t="s">
+      <c r="G17" s="74" t="s">
         <v>73</v>
       </c>
       <c r="H17" s="21" t="s">
@@ -2862,8 +2862,8 @@
       <c r="Z17" s="9"/>
     </row>
     <row r="18" spans="1:26" ht="102" customHeight="1">
-      <c r="A18" s="78"/>
-      <c r="B18" s="78"/>
+      <c r="A18" s="79"/>
+      <c r="B18" s="79"/>
       <c r="C18" s="58" t="s">
         <v>13</v>
       </c>
@@ -2876,7 +2876,7 @@
       <c r="F18" s="12">
         <v>45331</v>
       </c>
-      <c r="G18" s="78"/>
+      <c r="G18" s="79"/>
       <c r="H18" s="21" t="s">
         <v>74</v>
       </c>
@@ -2904,8 +2904,8 @@
       <c r="Z18" s="9"/>
     </row>
     <row r="19" spans="1:26" ht="78" customHeight="1">
-      <c r="A19" s="78"/>
-      <c r="B19" s="79"/>
+      <c r="A19" s="79"/>
+      <c r="B19" s="76"/>
       <c r="C19" s="58" t="s">
         <v>13</v>
       </c>
@@ -2918,7 +2918,7 @@
       <c r="F19" s="12">
         <v>45266</v>
       </c>
-      <c r="G19" s="78"/>
+      <c r="G19" s="79"/>
       <c r="H19" s="21" t="s">
         <v>79</v>
       </c>
@@ -3140,10 +3140,10 @@
       <c r="Z23" s="9"/>
     </row>
     <row r="24" spans="1:26" ht="124.5" customHeight="1">
-      <c r="A24" s="85" t="s">
+      <c r="A24" s="91" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="77" t="s">
+      <c r="B24" s="86" t="s">
         <v>111</v>
       </c>
       <c r="C24" s="61" t="s">
@@ -3158,14 +3158,14 @@
       <c r="F24" s="12">
         <v>44809</v>
       </c>
-      <c r="G24" s="80" t="s">
+      <c r="G24" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="89" t="s">
+      <c r="H24" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="I24" s="90"/>
-      <c r="J24" s="91"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="82"/>
       <c r="K24" s="15"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
@@ -3184,8 +3184,8 @@
       <c r="Z24" s="9"/>
     </row>
     <row r="25" spans="1:26" ht="70.5" customHeight="1">
-      <c r="A25" s="79"/>
-      <c r="B25" s="79"/>
+      <c r="A25" s="76"/>
+      <c r="B25" s="76"/>
       <c r="C25" s="58" t="s">
         <v>13</v>
       </c>
@@ -3198,10 +3198,10 @@
       <c r="F25" s="12">
         <v>45534</v>
       </c>
-      <c r="G25" s="79"/>
-      <c r="H25" s="92"/>
-      <c r="I25" s="93"/>
-      <c r="J25" s="94"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="85"/>
       <c r="K25" s="15"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
@@ -3241,10 +3241,10 @@
       <c r="G26" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="86" t="s">
+      <c r="H26" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="I26" s="76"/>
+      <c r="I26" s="73"/>
       <c r="J26" s="14"/>
       <c r="K26" s="15" t="s">
         <v>30</v>
@@ -3266,10 +3266,10 @@
       <c r="Z26" s="9"/>
     </row>
     <row r="27" spans="1:26" ht="267" customHeight="1">
-      <c r="A27" s="82" t="s">
+      <c r="A27" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="86" t="s">
         <v>124</v>
       </c>
       <c r="C27" s="58" t="s">
@@ -3284,16 +3284,16 @@
       <c r="F27" s="12">
         <v>45190</v>
       </c>
-      <c r="G27" s="77" t="s">
+      <c r="G27" s="86" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="77" t="s">
+      <c r="H27" s="86" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="95" t="s">
+      <c r="I27" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="95" t="s">
+      <c r="J27" s="87" t="s">
         <v>127</v>
       </c>
       <c r="K27" s="35"/>
@@ -3314,8 +3314,8 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="42.75">
-      <c r="A28" s="79"/>
-      <c r="B28" s="79"/>
+      <c r="A28" s="76"/>
+      <c r="B28" s="76"/>
       <c r="C28" s="58" t="s">
         <v>13</v>
       </c>
@@ -3328,10 +3328,10 @@
       <c r="F28" s="12">
         <v>45400</v>
       </c>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="76"/>
       <c r="K28" s="15"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
@@ -3731,7 +3731,9 @@
       <c r="E37" s="97" t="s">
         <v>313</v>
       </c>
-      <c r="F37" s="12"/>
+      <c r="F37" s="12">
+        <v>46059</v>
+      </c>
       <c r="G37" s="13" t="s">
         <v>187</v>
       </c>
@@ -4547,10 +4549,10 @@
       <c r="G56" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="H56" s="86" t="s">
+      <c r="H56" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="I56" s="76"/>
+      <c r="I56" s="73"/>
       <c r="J56" s="13" t="s">
         <v>300</v>
       </c>
@@ -31117,6 +31119,22 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
     <mergeCell ref="H56:I56"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="H13:H15"/>
@@ -31130,22 +31148,6 @@
     <mergeCell ref="H27:H28"/>
     <mergeCell ref="I27:I28"/>
     <mergeCell ref="J27:J28"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="I7:I10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D56" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -31234,6 +31236,7 @@
     <hyperlink ref="A54" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
     <hyperlink ref="A55" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
     <hyperlink ref="A56" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="E37" r:id="rId82" xr:uid="{BE8A3D1F-7217-4106-97EB-5926D8F6809C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/Analyses/Partner-Analyses-Metadata.xlsx
+++ b/Analyses/Partner-Analyses-Metadata.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/otss1968_ox_ac_uk/Documents/Documents/GitHub/CCP/Analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A05085-C896-4B7B-B1F1-F5B514CAA1E5}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F92EAD89-E1C6-457E-A5FC-99CE96A84EC7}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Partner Analyses" sheetId="1" r:id="rId1"/>
     <sheet name="Sub-processors" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partner Analyses'!$A$3:$Z$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partner Analyses'!$A$3:$Z$57</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="318">
   <si>
     <t>ISARIC Partner Analyses</t>
   </si>
@@ -1156,6 +1156,31 @@
   </si>
   <si>
     <t>Immune dysregulation through longitudinal lymphocyte trajectories and their clinical determinants in hospitalized COVID-19 patients</t>
+  </si>
+  <si>
+    <t>Scalable Analytical Methods</t>
+  </si>
+  <si>
+    <r>
+      <t>Reusable and Scalable Analytical Methods to Strengthen Clinical Research and Enable Agile, Coordinated Responses to Infectious Disease Threats</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Establish a reusable and scalable analytical framework within the ISARIC Clinical Epidemiology Platform to strengthen clinical research and support rapid, coordinated outbreak response.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esteban Garcia Gallo, University of Oxford, UK
+</t>
   </si>
 </sst>
 </file>
@@ -1170,11 +1195,18 @@
     <numFmt numFmtId="168" formatCode="ddmmmyyyy"/>
     <numFmt numFmtId="169" formatCode="dmmmyyyy"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1384,6 +1416,19 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1630,73 +1675,70 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1705,25 +1747,25 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1732,165 +1774,179 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2110,7 +2166,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1004"/>
+  <dimension ref="A1:Z1005"/>
   <sheetFormatPr defaultColWidth="14.46484375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="27.46484375" customWidth="1"/>
@@ -2126,18 +2182,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -2156,16 +2212,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="14.65" thickBot="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -2255,10 +2311,10 @@
       <c r="G4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="95" t="s">
+      <c r="H4" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="73"/>
+      <c r="I4" s="78"/>
       <c r="J4" s="14" t="s">
         <v>18</v>
       </c>
@@ -2301,10 +2357,10 @@
       <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="95" t="s">
+      <c r="H5" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="73"/>
+      <c r="I5" s="78"/>
       <c r="J5" s="14" t="s">
         <v>18</v>
       </c>
@@ -2378,10 +2434,10 @@
       <c r="Z6" s="9"/>
     </row>
     <row r="7" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="79" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="58" t="s">
@@ -2396,13 +2452,13 @@
       <c r="F7" s="12">
         <v>44540</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="77" t="s">
+      <c r="H7" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="77" t="s">
+      <c r="I7" s="83" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="19" t="s">
@@ -2426,8 +2482,8 @@
       <c r="Z7" s="9"/>
     </row>
     <row r="8" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A8" s="79"/>
-      <c r="B8" s="79"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="80"/>
       <c r="C8" s="58" t="s">
         <v>13</v>
       </c>
@@ -2440,9 +2496,9 @@
       <c r="F8" s="12">
         <v>44772</v>
       </c>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
       <c r="J8" s="19" t="s">
         <v>39</v>
       </c>
@@ -2464,8 +2520,8 @@
       <c r="Z8" s="9"/>
     </row>
     <row r="9" spans="1:26" ht="39.75" customHeight="1">
-      <c r="A9" s="79"/>
-      <c r="B9" s="79"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="80"/>
       <c r="C9" s="58" t="s">
         <v>13</v>
       </c>
@@ -2478,9 +2534,9 @@
       <c r="F9" s="12">
         <v>44817</v>
       </c>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
       <c r="J9" s="19" t="s">
         <v>39</v>
       </c>
@@ -2502,8 +2558,8 @@
       <c r="Z9" s="9"/>
     </row>
     <row r="10" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A10" s="76"/>
-      <c r="B10" s="76"/>
+      <c r="A10" s="81"/>
+      <c r="B10" s="81"/>
       <c r="C10" s="58" t="s">
         <v>13</v>
       </c>
@@ -2516,9 +2572,9 @@
       <c r="F10" s="12">
         <v>45055</v>
       </c>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="76"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
       <c r="J10" s="19" t="s">
         <v>39</v>
       </c>
@@ -2640,10 +2696,10 @@
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="79" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="60" t="s">
@@ -2658,16 +2714,16 @@
       <c r="F13" s="12">
         <v>44671</v>
       </c>
-      <c r="G13" s="74" t="s">
+      <c r="G13" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="74" t="s">
+      <c r="H13" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="74" t="s">
+      <c r="I13" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="77" t="s">
+      <c r="J13" s="83" t="s">
         <v>62</v>
       </c>
       <c r="K13" s="28">
@@ -2690,8 +2746,8 @@
       <c r="Z13" s="9"/>
     </row>
     <row r="14" spans="1:26" s="56" customFormat="1" ht="66.75" customHeight="1">
-      <c r="A14" s="89"/>
-      <c r="B14" s="90"/>
+      <c r="A14" s="85"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="58" t="s">
         <v>13</v>
       </c>
@@ -2704,10 +2760,10 @@
       <c r="F14" s="12">
         <v>45072</v>
       </c>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="78"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="90"/>
       <c r="K14" s="28"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
@@ -2726,8 +2782,8 @@
       <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="78.75" customHeight="1">
-      <c r="A15" s="76"/>
-      <c r="B15" s="76"/>
+      <c r="A15" s="81"/>
+      <c r="B15" s="81"/>
       <c r="C15" s="68" t="s">
         <v>13</v>
       </c>
@@ -2740,10 +2796,10 @@
       <c r="F15" s="71">
         <v>45981</v>
       </c>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="76"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
       <c r="K15" s="28"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -2812,10 +2868,10 @@
       <c r="Z16" s="9"/>
     </row>
     <row r="17" spans="1:26" ht="45" customHeight="1">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="79" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="58" t="s">
@@ -2830,7 +2886,7 @@
       <c r="F17" s="12">
         <v>44814</v>
       </c>
-      <c r="G17" s="74" t="s">
+      <c r="G17" s="82" t="s">
         <v>73</v>
       </c>
       <c r="H17" s="21" t="s">
@@ -2862,8 +2918,8 @@
       <c r="Z17" s="9"/>
     </row>
     <row r="18" spans="1:26" ht="102" customHeight="1">
-      <c r="A18" s="79"/>
-      <c r="B18" s="79"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="80"/>
       <c r="C18" s="58" t="s">
         <v>13</v>
       </c>
@@ -2876,7 +2932,7 @@
       <c r="F18" s="12">
         <v>45331</v>
       </c>
-      <c r="G18" s="79"/>
+      <c r="G18" s="80"/>
       <c r="H18" s="21" t="s">
         <v>74</v>
       </c>
@@ -2904,8 +2960,8 @@
       <c r="Z18" s="9"/>
     </row>
     <row r="19" spans="1:26" ht="78" customHeight="1">
-      <c r="A19" s="79"/>
-      <c r="B19" s="76"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="81"/>
       <c r="C19" s="58" t="s">
         <v>13</v>
       </c>
@@ -2918,7 +2974,7 @@
       <c r="F19" s="12">
         <v>45266</v>
       </c>
-      <c r="G19" s="79"/>
+      <c r="G19" s="80"/>
       <c r="H19" s="21" t="s">
         <v>79</v>
       </c>
@@ -3140,10 +3196,10 @@
       <c r="Z23" s="9"/>
     </row>
     <row r="24" spans="1:26" ht="124.5" customHeight="1">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="86" t="s">
+      <c r="B24" s="79" t="s">
         <v>111</v>
       </c>
       <c r="C24" s="61" t="s">
@@ -3158,14 +3214,14 @@
       <c r="F24" s="12">
         <v>44809</v>
       </c>
-      <c r="G24" s="74" t="s">
+      <c r="G24" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="80" t="s">
+      <c r="H24" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="I24" s="81"/>
-      <c r="J24" s="82"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="93"/>
       <c r="K24" s="15"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
@@ -3184,8 +3240,8 @@
       <c r="Z24" s="9"/>
     </row>
     <row r="25" spans="1:26" ht="70.5" customHeight="1">
-      <c r="A25" s="76"/>
-      <c r="B25" s="76"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="81"/>
       <c r="C25" s="58" t="s">
         <v>13</v>
       </c>
@@ -3198,10 +3254,10 @@
       <c r="F25" s="12">
         <v>45534</v>
       </c>
-      <c r="G25" s="76"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="85"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="96"/>
       <c r="K25" s="15"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
@@ -3241,10 +3297,10 @@
       <c r="G26" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="72" t="s">
+      <c r="H26" s="88" t="s">
         <v>122</v>
       </c>
-      <c r="I26" s="73"/>
+      <c r="I26" s="78"/>
       <c r="J26" s="14"/>
       <c r="K26" s="15" t="s">
         <v>30</v>
@@ -3266,10 +3322,10 @@
       <c r="Z26" s="9"/>
     </row>
     <row r="27" spans="1:26" ht="267" customHeight="1">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="86" t="s">
+      <c r="B27" s="79" t="s">
         <v>124</v>
       </c>
       <c r="C27" s="58" t="s">
@@ -3284,16 +3340,16 @@
       <c r="F27" s="12">
         <v>45190</v>
       </c>
-      <c r="G27" s="86" t="s">
+      <c r="G27" s="79" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="86" t="s">
+      <c r="H27" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="87" t="s">
+      <c r="I27" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="87" t="s">
+      <c r="J27" s="97" t="s">
         <v>127</v>
       </c>
       <c r="K27" s="35"/>
@@ -3314,8 +3370,8 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="42.75">
-      <c r="A28" s="76"/>
-      <c r="B28" s="76"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="81"/>
       <c r="C28" s="58" t="s">
         <v>13</v>
       </c>
@@ -3328,10 +3384,10 @@
       <c r="F28" s="12">
         <v>45400</v>
       </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="76"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
       <c r="K28" s="15"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
@@ -3728,7 +3784,7 @@
       <c r="D37" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="97" t="s">
+      <c r="E37" s="73" t="s">
         <v>313</v>
       </c>
       <c r="F37" s="12">
@@ -4315,25 +4371,25 @@
       <c r="Y50" s="9"/>
       <c r="Z50" s="9"/>
     </row>
-    <row r="51" spans="1:26" ht="57">
-      <c r="A51" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="C51" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51" s="45" t="s">
-        <v>226</v>
+    <row r="51" spans="1:26" s="72" customFormat="1" ht="71.25">
+      <c r="A51" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="B51" s="99" t="s">
+        <v>315</v>
+      </c>
+      <c r="C51" s="58"/>
+      <c r="D51" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="E51" s="17"/>
       <c r="F51" s="12"/>
-      <c r="G51" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="H51" s="13"/>
+      <c r="G51" s="100" t="s">
+        <v>316</v>
+      </c>
+      <c r="H51" s="101" t="s">
+        <v>317</v>
+      </c>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
       <c r="K51" s="15"/>
@@ -4354,32 +4410,26 @@
       <c r="Z51" s="9"/>
     </row>
     <row r="52" spans="1:26" ht="57">
-      <c r="A52" s="18" t="s">
-        <v>270</v>
+      <c r="A52" s="13" t="s">
+        <v>267</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C52" s="62"/>
+        <v>268</v>
+      </c>
+      <c r="C52" s="58" t="s">
+        <v>18</v>
+      </c>
       <c r="D52" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="E52" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="46"/>
+        <v>226</v>
+      </c>
+      <c r="E52" s="17"/>
+      <c r="F52" s="12"/>
       <c r="G52" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H52" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>276</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
       <c r="K52" s="15"/>
       <c r="L52" s="9"/>
       <c r="M52" s="9"/>
@@ -4397,12 +4447,12 @@
       <c r="Y52" s="9"/>
       <c r="Z52" s="9"/>
     </row>
-    <row r="53" spans="1:26" ht="156.75">
+    <row r="53" spans="1:26" ht="57">
       <c r="A53" s="18" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C53" s="62"/>
       <c r="D53" s="45" t="s">
@@ -4413,16 +4463,16 @@
       </c>
       <c r="F53" s="46"/>
       <c r="G53" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K53" s="15"/>
       <c r="L53" s="9"/>
@@ -4441,12 +4491,12 @@
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
     </row>
-    <row r="54" spans="1:26" ht="71.25">
+    <row r="54" spans="1:26" ht="156.75">
       <c r="A54" s="18" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C54" s="62"/>
       <c r="D54" s="45" t="s">
@@ -4457,20 +4507,18 @@
       </c>
       <c r="F54" s="46"/>
       <c r="G54" s="13" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="K54" s="47">
-        <v>44213</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="K54" s="15"/>
       <c r="L54" s="9"/>
       <c r="M54" s="9"/>
       <c r="N54" s="9"/>
@@ -4487,12 +4535,12 @@
       <c r="Y54" s="9"/>
       <c r="Z54" s="9"/>
     </row>
-    <row r="55" spans="1:26" ht="96.75" customHeight="1">
+    <row r="55" spans="1:26" ht="71.25">
       <c r="A55" s="18" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C55" s="62"/>
       <c r="D55" s="45" t="s">
@@ -4503,18 +4551,20 @@
       </c>
       <c r="F55" s="46"/>
       <c r="G55" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="H55" s="19" t="s">
-        <v>292</v>
+        <v>285</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>286</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="K55" s="15"/>
+        <v>288</v>
+      </c>
+      <c r="K55" s="47">
+        <v>44213</v>
+      </c>
       <c r="L55" s="9"/>
       <c r="M55" s="9"/>
       <c r="N55" s="9"/>
@@ -4531,32 +4581,34 @@
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
     </row>
-    <row r="56" spans="1:26" ht="180" customHeight="1">
+    <row r="56" spans="1:26" ht="96.75" customHeight="1">
       <c r="A56" s="18" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C56" s="62"/>
       <c r="D56" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>297</v>
+        <v>13</v>
       </c>
       <c r="F56" s="46"/>
       <c r="G56" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="H56" s="72" t="s">
-        <v>299</v>
-      </c>
-      <c r="I56" s="73"/>
+        <v>291</v>
+      </c>
+      <c r="H56" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>293</v>
+      </c>
       <c r="J56" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="K56" s="48"/>
+        <v>294</v>
+      </c>
+      <c r="K56" s="15"/>
       <c r="L56" s="9"/>
       <c r="M56" s="9"/>
       <c r="N56" s="9"/>
@@ -4573,18 +4625,32 @@
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
     </row>
-    <row r="57" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A57" s="49"/>
-      <c r="B57" s="50"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="51"/>
-      <c r="G57" s="52"/>
-      <c r="H57" s="52"/>
-      <c r="I57" s="52"/>
-      <c r="J57" s="52"/>
-      <c r="K57" s="53"/>
+    <row r="57" spans="1:26" ht="180" customHeight="1">
+      <c r="A57" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C57" s="62"/>
+      <c r="D57" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E57" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="F57" s="46"/>
+      <c r="G57" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="H57" s="88" t="s">
+        <v>299</v>
+      </c>
+      <c r="I57" s="78"/>
+      <c r="J57" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="K57" s="48"/>
       <c r="L57" s="9"/>
       <c r="M57" s="9"/>
       <c r="N57" s="9"/>
@@ -4602,7 +4668,7 @@
       <c r="Z57" s="9"/>
     </row>
     <row r="58" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A58" s="54"/>
+      <c r="A58" s="49"/>
       <c r="B58" s="50"/>
       <c r="C58" s="63"/>
       <c r="D58" s="50"/>
@@ -4691,7 +4757,7 @@
       <c r="C61" s="63"/>
       <c r="D61" s="50"/>
       <c r="E61" s="50"/>
-      <c r="F61" s="55"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="52"/>
       <c r="H61" s="52"/>
       <c r="I61" s="52"/>
@@ -9278,7 +9344,7 @@
       <c r="Z224" s="9"/>
     </row>
     <row r="225" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A225" s="9"/>
+      <c r="A225" s="54"/>
       <c r="B225" s="50"/>
       <c r="C225" s="63"/>
       <c r="D225" s="50"/>
@@ -31117,25 +31183,37 @@
       <c r="Y1004" s="9"/>
       <c r="Z1004" s="9"/>
     </row>
+    <row r="1005" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A1005" s="9"/>
+      <c r="B1005" s="50"/>
+      <c r="C1005" s="63"/>
+      <c r="D1005" s="50"/>
+      <c r="E1005" s="50"/>
+      <c r="F1005" s="55"/>
+      <c r="G1005" s="52"/>
+      <c r="H1005" s="52"/>
+      <c r="I1005" s="52"/>
+      <c r="J1005" s="52"/>
+      <c r="K1005" s="53"/>
+      <c r="L1005" s="9"/>
+      <c r="M1005" s="9"/>
+      <c r="N1005" s="9"/>
+      <c r="O1005" s="9"/>
+      <c r="P1005" s="9"/>
+      <c r="Q1005" s="9"/>
+      <c r="R1005" s="9"/>
+      <c r="S1005" s="9"/>
+      <c r="T1005" s="9"/>
+      <c r="U1005" s="9"/>
+      <c r="V1005" s="9"/>
+      <c r="W1005" s="9"/>
+      <c r="X1005" s="9"/>
+      <c r="Y1005" s="9"/>
+      <c r="Z1005" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="I7:I10"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="I13:I15"/>
@@ -31148,9 +31226,25 @@
     <mergeCell ref="H27:H28"/>
     <mergeCell ref="I27:I28"/>
     <mergeCell ref="J27:J28"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D56" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D57" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Published,Awaiting publication,Analysis underway,Analysis completed,On hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -31231,12 +31325,13 @@
     <hyperlink ref="C47" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
     <hyperlink ref="A48" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
     <hyperlink ref="A49" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="A52" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="A53" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="A54" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="A55" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="A56" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="E37" r:id="rId82" xr:uid="{BE8A3D1F-7217-4106-97EB-5926D8F6809C}"/>
+    <hyperlink ref="A53" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="A55" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="A56" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="E37" r:id="rId80" xr:uid="{BE8A3D1F-7217-4106-97EB-5926D8F6809C}"/>
+    <hyperlink ref="A51" r:id="rId81" xr:uid="{4C5DAD40-0EE6-4723-9972-DED6C1C412C8}"/>
+    <hyperlink ref="A54" r:id="rId82" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="A57" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -31255,13 +31350,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="98" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
       <c r="A2" s="56"/>

--- a/Analyses/Partner-Analyses-Metadata.xlsx
+++ b/Analyses/Partner-Analyses-Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/otss1968_ox_ac_uk/Documents/Documents/GitHub/CCP/Analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F92EAD89-E1C6-457E-A5FC-99CE96A84EC7}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{776556D4-255E-4DA2-90ED-E95B1DE49977}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sub-processors" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partner Analyses'!$A$3:$Z$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partner Analyses'!$A$3:$Z$58</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="322">
   <si>
     <t>ISARIC Partner Analyses</t>
   </si>
@@ -1182,6 +1182,18 @@
     <t xml:space="preserve">Esteban Garcia Gallo, University of Oxford, UK
 </t>
   </si>
+  <si>
+    <t>Steroid Outcomes by Income Level</t>
+  </si>
+  <si>
+    <t>Global Differences in Systemic Corticosteroid Treatment Pathways and Clinical Outcomes Among Hospitalized COVID-19 Patients Across Income-Level Settings</t>
+  </si>
+  <si>
+    <t>This study aims to examine how corticosteroid treatment for hospitalised COVID-19 patients differs between high-income countries (HICs) and low- and middle-income countries (LMICs). It focuses on variations in use, timing, duration, and integration into care pathways, and evaluates how these differences are associated with clinical outcomes using large international datasets.</t>
+  </si>
+  <si>
+    <t>Zainab KA Alaraji, Alnahrain University College of medicine, Iraq.</t>
+  </si>
 </sst>
 </file>
 
@@ -1195,11 +1207,18 @@
     <numFmt numFmtId="168" formatCode="ddmmmyyyy"/>
     <numFmt numFmtId="169" formatCode="dmmmyyyy"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1426,6 +1445,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1675,73 +1701,70 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1750,25 +1773,25 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1777,176 +1800,189 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2166,10 +2202,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1005"/>
+  <dimension ref="A1:Z1006"/>
   <sheetFormatPr defaultColWidth="14.46484375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.46484375" customWidth="1"/>
+    <col min="1" max="1" width="44.265625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="42.265625" style="64" customWidth="1"/>
     <col min="4" max="4" width="24.46484375" customWidth="1"/>
@@ -2182,18 +2218,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -2212,16 +2248,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="14.65" thickBot="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="A2" s="101"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -2311,10 +2347,10 @@
       <c r="G4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="77" t="s">
+      <c r="H4" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="78"/>
+      <c r="I4" s="80"/>
       <c r="J4" s="14" t="s">
         <v>18</v>
       </c>
@@ -2357,10 +2393,10 @@
       <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="77" t="s">
+      <c r="H5" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="78"/>
+      <c r="I5" s="80"/>
       <c r="J5" s="14" t="s">
         <v>18</v>
       </c>
@@ -2434,10 +2470,10 @@
       <c r="Z6" s="9"/>
     </row>
     <row r="7" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="93" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="58" t="s">
@@ -2452,13 +2488,13 @@
       <c r="F7" s="12">
         <v>44540</v>
       </c>
-      <c r="G7" s="82" t="s">
+      <c r="G7" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="83" t="s">
+      <c r="H7" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="83" t="s">
+      <c r="I7" s="84" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="19" t="s">
@@ -2482,8 +2518,8 @@
       <c r="Z7" s="9"/>
     </row>
     <row r="8" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A8" s="80"/>
-      <c r="B8" s="80"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="86"/>
       <c r="C8" s="58" t="s">
         <v>13</v>
       </c>
@@ -2496,9 +2532,9 @@
       <c r="F8" s="12">
         <v>44772</v>
       </c>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
       <c r="J8" s="19" t="s">
         <v>39</v>
       </c>
@@ -2520,8 +2556,8 @@
       <c r="Z8" s="9"/>
     </row>
     <row r="9" spans="1:26" ht="39.75" customHeight="1">
-      <c r="A9" s="80"/>
-      <c r="B9" s="80"/>
+      <c r="A9" s="86"/>
+      <c r="B9" s="86"/>
       <c r="C9" s="58" t="s">
         <v>13</v>
       </c>
@@ -2534,9 +2570,9 @@
       <c r="F9" s="12">
         <v>44817</v>
       </c>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
       <c r="J9" s="19" t="s">
         <v>39</v>
       </c>
@@ -2558,8 +2594,8 @@
       <c r="Z9" s="9"/>
     </row>
     <row r="10" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="81"/>
+      <c r="A10" s="83"/>
+      <c r="B10" s="83"/>
       <c r="C10" s="58" t="s">
         <v>13</v>
       </c>
@@ -2572,9 +2608,9 @@
       <c r="F10" s="12">
         <v>45055</v>
       </c>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
       <c r="J10" s="19" t="s">
         <v>39</v>
       </c>
@@ -2696,10 +2732,10 @@
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="93" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="60" t="s">
@@ -2714,16 +2750,16 @@
       <c r="F13" s="12">
         <v>44671</v>
       </c>
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="82" t="s">
+      <c r="H13" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="82" t="s">
+      <c r="I13" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="83" t="s">
+      <c r="J13" s="84" t="s">
         <v>62</v>
       </c>
       <c r="K13" s="28">
@@ -2746,8 +2782,8 @@
       <c r="Z13" s="9"/>
     </row>
     <row r="14" spans="1:26" s="56" customFormat="1" ht="66.75" customHeight="1">
-      <c r="A14" s="85"/>
-      <c r="B14" s="86"/>
+      <c r="A14" s="96"/>
+      <c r="B14" s="97"/>
       <c r="C14" s="58" t="s">
         <v>13</v>
       </c>
@@ -2760,10 +2796,10 @@
       <c r="F14" s="12">
         <v>45072</v>
       </c>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="90"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="85"/>
       <c r="K14" s="28"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
@@ -2782,8 +2818,8 @@
       <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="78.75" customHeight="1">
-      <c r="A15" s="81"/>
-      <c r="B15" s="81"/>
+      <c r="A15" s="83"/>
+      <c r="B15" s="83"/>
       <c r="C15" s="68" t="s">
         <v>13</v>
       </c>
@@ -2796,10 +2832,10 @@
       <c r="F15" s="71">
         <v>45981</v>
       </c>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
       <c r="K15" s="28"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -2868,10 +2904,10 @@
       <c r="Z16" s="9"/>
     </row>
     <row r="17" spans="1:26" ht="45" customHeight="1">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="79" t="s">
+      <c r="B17" s="93" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="58" t="s">
@@ -2886,7 +2922,7 @@
       <c r="F17" s="12">
         <v>44814</v>
       </c>
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="81" t="s">
         <v>73</v>
       </c>
       <c r="H17" s="21" t="s">
@@ -2918,8 +2954,8 @@
       <c r="Z17" s="9"/>
     </row>
     <row r="18" spans="1:26" ht="102" customHeight="1">
-      <c r="A18" s="80"/>
-      <c r="B18" s="80"/>
+      <c r="A18" s="86"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="58" t="s">
         <v>13</v>
       </c>
@@ -2932,7 +2968,7 @@
       <c r="F18" s="12">
         <v>45331</v>
       </c>
-      <c r="G18" s="80"/>
+      <c r="G18" s="86"/>
       <c r="H18" s="21" t="s">
         <v>74</v>
       </c>
@@ -2960,8 +2996,8 @@
       <c r="Z18" s="9"/>
     </row>
     <row r="19" spans="1:26" ht="78" customHeight="1">
-      <c r="A19" s="80"/>
-      <c r="B19" s="81"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="83"/>
       <c r="C19" s="58" t="s">
         <v>13</v>
       </c>
@@ -2974,7 +3010,7 @@
       <c r="F19" s="12">
         <v>45266</v>
       </c>
-      <c r="G19" s="80"/>
+      <c r="G19" s="86"/>
       <c r="H19" s="21" t="s">
         <v>79</v>
       </c>
@@ -3196,10 +3232,10 @@
       <c r="Z23" s="9"/>
     </row>
     <row r="24" spans="1:26" ht="124.5" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="98" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="93" t="s">
         <v>111</v>
       </c>
       <c r="C24" s="61" t="s">
@@ -3214,14 +3250,14 @@
       <c r="F24" s="12">
         <v>44809</v>
       </c>
-      <c r="G24" s="82" t="s">
+      <c r="G24" s="81" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="91" t="s">
+      <c r="H24" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="I24" s="92"/>
-      <c r="J24" s="93"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="89"/>
       <c r="K24" s="15"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
@@ -3240,8 +3276,8 @@
       <c r="Z24" s="9"/>
     </row>
     <row r="25" spans="1:26" ht="70.5" customHeight="1">
-      <c r="A25" s="81"/>
-      <c r="B25" s="81"/>
+      <c r="A25" s="83"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="58" t="s">
         <v>13</v>
       </c>
@@ -3254,10 +3290,10 @@
       <c r="F25" s="12">
         <v>45534</v>
       </c>
-      <c r="G25" s="81"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="96"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="92"/>
       <c r="K25" s="15"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
@@ -3297,10 +3333,10 @@
       <c r="G26" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="88" t="s">
+      <c r="H26" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="I26" s="78"/>
+      <c r="I26" s="80"/>
       <c r="J26" s="14"/>
       <c r="K26" s="15" t="s">
         <v>30</v>
@@ -3322,10 +3358,10 @@
       <c r="Z26" s="9"/>
     </row>
     <row r="27" spans="1:26" ht="267" customHeight="1">
-      <c r="A27" s="84" t="s">
+      <c r="A27" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="79" t="s">
+      <c r="B27" s="93" t="s">
         <v>124</v>
       </c>
       <c r="C27" s="58" t="s">
@@ -3340,16 +3376,16 @@
       <c r="F27" s="12">
         <v>45190</v>
       </c>
-      <c r="G27" s="79" t="s">
+      <c r="G27" s="93" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="79" t="s">
+      <c r="H27" s="93" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="97" t="s">
+      <c r="I27" s="94" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="97" t="s">
+      <c r="J27" s="94" t="s">
         <v>127</v>
       </c>
       <c r="K27" s="35"/>
@@ -3370,8 +3406,8 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="42.75">
-      <c r="A28" s="81"/>
-      <c r="B28" s="81"/>
+      <c r="A28" s="83"/>
+      <c r="B28" s="83"/>
       <c r="C28" s="58" t="s">
         <v>13</v>
       </c>
@@ -3384,10 +3420,10 @@
       <c r="F28" s="12">
         <v>45400</v>
       </c>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="81"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
       <c r="K28" s="15"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
@@ -4372,10 +4408,10 @@
       <c r="Z50" s="9"/>
     </row>
     <row r="51" spans="1:26" s="72" customFormat="1" ht="71.25">
-      <c r="A51" s="102" t="s">
+      <c r="A51" s="78" t="s">
         <v>314</v>
       </c>
-      <c r="B51" s="99" t="s">
+      <c r="B51" s="75" t="s">
         <v>315</v>
       </c>
       <c r="C51" s="58"/>
@@ -4384,10 +4420,10 @@
       </c>
       <c r="E51" s="17"/>
       <c r="F51" s="12"/>
-      <c r="G51" s="100" t="s">
+      <c r="G51" s="76" t="s">
         <v>316</v>
       </c>
-      <c r="H51" s="101" t="s">
+      <c r="H51" s="77" t="s">
         <v>317</v>
       </c>
       <c r="I51" s="13"/>
@@ -4409,25 +4445,25 @@
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
     </row>
-    <row r="52" spans="1:26" ht="57">
-      <c r="A52" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="C52" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="D52" s="45" t="s">
-        <v>226</v>
+    <row r="52" spans="1:26" s="74" customFormat="1" ht="84" customHeight="1">
+      <c r="A52" s="106" t="s">
+        <v>318</v>
+      </c>
+      <c r="B52" s="75" t="s">
+        <v>319</v>
+      </c>
+      <c r="C52" s="58"/>
+      <c r="D52" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="E52" s="17"/>
       <c r="F52" s="12"/>
-      <c r="G52" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="H52" s="13"/>
+      <c r="G52" s="104" t="s">
+        <v>320</v>
+      </c>
+      <c r="H52" s="105" t="s">
+        <v>321</v>
+      </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
       <c r="K52" s="15"/>
@@ -4448,32 +4484,26 @@
       <c r="Z52" s="9"/>
     </row>
     <row r="53" spans="1:26" ht="57">
-      <c r="A53" s="18" t="s">
-        <v>270</v>
+      <c r="A53" s="13" t="s">
+        <v>267</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C53" s="62"/>
+        <v>268</v>
+      </c>
+      <c r="C53" s="58" t="s">
+        <v>18</v>
+      </c>
       <c r="D53" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="E53" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="46"/>
+        <v>226</v>
+      </c>
+      <c r="E53" s="17"/>
+      <c r="F53" s="12"/>
       <c r="G53" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>276</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
       <c r="K53" s="15"/>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
@@ -4491,12 +4521,12 @@
       <c r="Y53" s="9"/>
       <c r="Z53" s="9"/>
     </row>
-    <row r="54" spans="1:26" ht="156.75">
+    <row r="54" spans="1:26" ht="57">
       <c r="A54" s="18" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C54" s="62"/>
       <c r="D54" s="45" t="s">
@@ -4507,16 +4537,16 @@
       </c>
       <c r="F54" s="46"/>
       <c r="G54" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K54" s="15"/>
       <c r="L54" s="9"/>
@@ -4535,12 +4565,12 @@
       <c r="Y54" s="9"/>
       <c r="Z54" s="9"/>
     </row>
-    <row r="55" spans="1:26" ht="71.25">
+    <row r="55" spans="1:26" ht="156.75">
       <c r="A55" s="18" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C55" s="62"/>
       <c r="D55" s="45" t="s">
@@ -4551,20 +4581,18 @@
       </c>
       <c r="F55" s="46"/>
       <c r="G55" s="13" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="K55" s="47">
-        <v>44213</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="K55" s="15"/>
       <c r="L55" s="9"/>
       <c r="M55" s="9"/>
       <c r="N55" s="9"/>
@@ -4581,12 +4609,12 @@
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
     </row>
-    <row r="56" spans="1:26" ht="96.75" customHeight="1">
+    <row r="56" spans="1:26" ht="71.25">
       <c r="A56" s="18" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C56" s="62"/>
       <c r="D56" s="45" t="s">
@@ -4597,18 +4625,20 @@
       </c>
       <c r="F56" s="46"/>
       <c r="G56" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>292</v>
+        <v>285</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>286</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="K56" s="15"/>
+        <v>288</v>
+      </c>
+      <c r="K56" s="47">
+        <v>44213</v>
+      </c>
       <c r="L56" s="9"/>
       <c r="M56" s="9"/>
       <c r="N56" s="9"/>
@@ -4625,32 +4655,34 @@
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
     </row>
-    <row r="57" spans="1:26" ht="180" customHeight="1">
+    <row r="57" spans="1:26" ht="96.75" customHeight="1">
       <c r="A57" s="18" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C57" s="62"/>
       <c r="D57" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>297</v>
+        <v>13</v>
       </c>
       <c r="F57" s="46"/>
       <c r="G57" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="H57" s="88" t="s">
-        <v>299</v>
-      </c>
-      <c r="I57" s="78"/>
+        <v>291</v>
+      </c>
+      <c r="H57" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>293</v>
+      </c>
       <c r="J57" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="K57" s="48"/>
+        <v>294</v>
+      </c>
+      <c r="K57" s="15"/>
       <c r="L57" s="9"/>
       <c r="M57" s="9"/>
       <c r="N57" s="9"/>
@@ -4667,18 +4699,32 @@
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
     </row>
-    <row r="58" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A58" s="49"/>
-      <c r="B58" s="50"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="51"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="52"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
-      <c r="K58" s="53"/>
+    <row r="58" spans="1:26" ht="180" customHeight="1">
+      <c r="A58" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C58" s="62"/>
+      <c r="D58" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E58" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="F58" s="46"/>
+      <c r="G58" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="H58" s="79" t="s">
+        <v>299</v>
+      </c>
+      <c r="I58" s="80"/>
+      <c r="J58" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="K58" s="48"/>
       <c r="L58" s="9"/>
       <c r="M58" s="9"/>
       <c r="N58" s="9"/>
@@ -4696,7 +4742,7 @@
       <c r="Z58" s="9"/>
     </row>
     <row r="59" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A59" s="54"/>
+      <c r="A59" s="49"/>
       <c r="B59" s="50"/>
       <c r="C59" s="63"/>
       <c r="D59" s="50"/>
@@ -4785,7 +4831,7 @@
       <c r="C62" s="63"/>
       <c r="D62" s="50"/>
       <c r="E62" s="50"/>
-      <c r="F62" s="55"/>
+      <c r="F62" s="51"/>
       <c r="G62" s="52"/>
       <c r="H62" s="52"/>
       <c r="I62" s="52"/>
@@ -9372,7 +9418,7 @@
       <c r="Z225" s="9"/>
     </row>
     <row r="226" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A226" s="9"/>
+      <c r="A226" s="54"/>
       <c r="B226" s="50"/>
       <c r="C226" s="63"/>
       <c r="D226" s="50"/>
@@ -31211,9 +31257,53 @@
       <c r="Y1005" s="9"/>
       <c r="Z1005" s="9"/>
     </row>
+    <row r="1006" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A1006" s="9"/>
+      <c r="B1006" s="50"/>
+      <c r="C1006" s="63"/>
+      <c r="D1006" s="50"/>
+      <c r="E1006" s="50"/>
+      <c r="F1006" s="55"/>
+      <c r="G1006" s="52"/>
+      <c r="H1006" s="52"/>
+      <c r="I1006" s="52"/>
+      <c r="J1006" s="52"/>
+      <c r="K1006" s="53"/>
+      <c r="L1006" s="9"/>
+      <c r="M1006" s="9"/>
+      <c r="N1006" s="9"/>
+      <c r="O1006" s="9"/>
+      <c r="P1006" s="9"/>
+      <c r="Q1006" s="9"/>
+      <c r="R1006" s="9"/>
+      <c r="S1006" s="9"/>
+      <c r="T1006" s="9"/>
+      <c r="U1006" s="9"/>
+      <c r="V1006" s="9"/>
+      <c r="W1006" s="9"/>
+      <c r="X1006" s="9"/>
+      <c r="Y1006" s="9"/>
+      <c r="Z1006" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="H58:I58"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="I13:I15"/>
@@ -31226,25 +31316,9 @@
     <mergeCell ref="H27:H28"/>
     <mergeCell ref="I27:I28"/>
     <mergeCell ref="J27:J28"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="I7:I10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D57" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D58" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Published,Awaiting publication,Analysis underway,Analysis completed,On hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -31325,13 +31399,14 @@
     <hyperlink ref="C47" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
     <hyperlink ref="A48" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
     <hyperlink ref="A49" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="A53" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="A55" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="A56" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="A54" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="A56" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="A57" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
     <hyperlink ref="E37" r:id="rId80" xr:uid="{BE8A3D1F-7217-4106-97EB-5926D8F6809C}"/>
     <hyperlink ref="A51" r:id="rId81" xr:uid="{4C5DAD40-0EE6-4723-9972-DED6C1C412C8}"/>
-    <hyperlink ref="A54" r:id="rId82" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="A57" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="A55" r:id="rId82" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="A58" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="A52" r:id="rId84" xr:uid="{AA4B0A3B-EFF0-43D2-8F6E-DAFE3F1EE47E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -31350,13 +31425,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="103" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
       <c r="A2" s="56"/>

--- a/Analyses/Partner-Analyses-Metadata.xlsx
+++ b/Analyses/Partner-Analyses-Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/otss1968_ox_ac_uk/Documents/Documents/GitHub/CCP/Analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{776556D4-255E-4DA2-90ED-E95B1DE49977}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A09F8105-248B-4F6F-99B9-1D3D44B1EB6A}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1703,7 +1703,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1919,36 +1919,33 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1963,26 +1960,30 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2218,18 +2219,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -2248,16 +2249,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="14.65" thickBot="1">
-      <c r="A2" s="101"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -2347,10 +2348,10 @@
       <c r="G4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="102" t="s">
+      <c r="H4" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="80"/>
+      <c r="I4" s="86"/>
       <c r="J4" s="14" t="s">
         <v>18</v>
       </c>
@@ -2393,10 +2394,10 @@
       <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="102" t="s">
+      <c r="H5" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="80"/>
+      <c r="I5" s="86"/>
       <c r="J5" s="14" t="s">
         <v>18</v>
       </c>
@@ -2470,10 +2471,10 @@
       <c r="Z6" s="9"/>
     </row>
     <row r="7" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A7" s="95" t="s">
+      <c r="A7" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="93" t="s">
+      <c r="B7" s="87" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="58" t="s">
@@ -2488,13 +2489,13 @@
       <c r="F7" s="12">
         <v>44540</v>
       </c>
-      <c r="G7" s="81" t="s">
+      <c r="G7" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="84" t="s">
+      <c r="H7" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="84" t="s">
+      <c r="I7" s="91" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="19" t="s">
@@ -2518,8 +2519,8 @@
       <c r="Z7" s="9"/>
     </row>
     <row r="8" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A8" s="86"/>
-      <c r="B8" s="86"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="88"/>
       <c r="C8" s="58" t="s">
         <v>13</v>
       </c>
@@ -2532,9 +2533,9 @@
       <c r="F8" s="12">
         <v>44772</v>
       </c>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
       <c r="J8" s="19" t="s">
         <v>39</v>
       </c>
@@ -2556,8 +2557,8 @@
       <c r="Z8" s="9"/>
     </row>
     <row r="9" spans="1:26" ht="39.75" customHeight="1">
-      <c r="A9" s="86"/>
-      <c r="B9" s="86"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="58" t="s">
         <v>13</v>
       </c>
@@ -2570,9 +2571,9 @@
       <c r="F9" s="12">
         <v>44817</v>
       </c>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
       <c r="J9" s="19" t="s">
         <v>39</v>
       </c>
@@ -2594,8 +2595,8 @@
       <c r="Z9" s="9"/>
     </row>
     <row r="10" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A10" s="83"/>
-      <c r="B10" s="83"/>
+      <c r="A10" s="89"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="58" t="s">
         <v>13</v>
       </c>
@@ -2608,9 +2609,9 @@
       <c r="F10" s="12">
         <v>45055</v>
       </c>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
       <c r="J10" s="19" t="s">
         <v>39</v>
       </c>
@@ -2732,10 +2733,10 @@
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A13" s="95" t="s">
+      <c r="A13" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="93" t="s">
+      <c r="B13" s="87" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="60" t="s">
@@ -2750,16 +2751,16 @@
       <c r="F13" s="12">
         <v>44671</v>
       </c>
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="81" t="s">
+      <c r="H13" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="81" t="s">
+      <c r="I13" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="84" t="s">
+      <c r="J13" s="91" t="s">
         <v>62</v>
       </c>
       <c r="K13" s="28">
@@ -2782,8 +2783,8 @@
       <c r="Z13" s="9"/>
     </row>
     <row r="14" spans="1:26" s="56" customFormat="1" ht="66.75" customHeight="1">
-      <c r="A14" s="96"/>
-      <c r="B14" s="97"/>
+      <c r="A14" s="93"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="58" t="s">
         <v>13</v>
       </c>
@@ -2796,10 +2797,10 @@
       <c r="F14" s="12">
         <v>45072</v>
       </c>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="85"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="98"/>
       <c r="K14" s="28"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
@@ -2818,8 +2819,8 @@
       <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="78.75" customHeight="1">
-      <c r="A15" s="83"/>
-      <c r="B15" s="83"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="89"/>
       <c r="C15" s="68" t="s">
         <v>13</v>
       </c>
@@ -2832,10 +2833,10 @@
       <c r="F15" s="71">
         <v>45981</v>
       </c>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
       <c r="K15" s="28"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -2904,10 +2905,10 @@
       <c r="Z16" s="9"/>
     </row>
     <row r="17" spans="1:26" ht="45" customHeight="1">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="93" t="s">
+      <c r="B17" s="87" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="58" t="s">
@@ -2922,7 +2923,7 @@
       <c r="F17" s="12">
         <v>44814</v>
       </c>
-      <c r="G17" s="81" t="s">
+      <c r="G17" s="90" t="s">
         <v>73</v>
       </c>
       <c r="H17" s="21" t="s">
@@ -2954,8 +2955,8 @@
       <c r="Z17" s="9"/>
     </row>
     <row r="18" spans="1:26" ht="102" customHeight="1">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="58" t="s">
         <v>13</v>
       </c>
@@ -2968,7 +2969,7 @@
       <c r="F18" s="12">
         <v>45331</v>
       </c>
-      <c r="G18" s="86"/>
+      <c r="G18" s="88"/>
       <c r="H18" s="21" t="s">
         <v>74</v>
       </c>
@@ -2996,8 +2997,8 @@
       <c r="Z18" s="9"/>
     </row>
     <row r="19" spans="1:26" ht="78" customHeight="1">
-      <c r="A19" s="86"/>
-      <c r="B19" s="83"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="89"/>
       <c r="C19" s="58" t="s">
         <v>13</v>
       </c>
@@ -3010,7 +3011,7 @@
       <c r="F19" s="12">
         <v>45266</v>
       </c>
-      <c r="G19" s="86"/>
+      <c r="G19" s="88"/>
       <c r="H19" s="21" t="s">
         <v>79</v>
       </c>
@@ -3232,10 +3233,10 @@
       <c r="Z23" s="9"/>
     </row>
     <row r="24" spans="1:26" ht="124.5" customHeight="1">
-      <c r="A24" s="98" t="s">
+      <c r="A24" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="93" t="s">
+      <c r="B24" s="87" t="s">
         <v>111</v>
       </c>
       <c r="C24" s="61" t="s">
@@ -3250,14 +3251,14 @@
       <c r="F24" s="12">
         <v>44809</v>
       </c>
-      <c r="G24" s="81" t="s">
+      <c r="G24" s="90" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="87" t="s">
+      <c r="H24" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="I24" s="88"/>
-      <c r="J24" s="89"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="101"/>
       <c r="K24" s="15"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
@@ -3276,8 +3277,8 @@
       <c r="Z24" s="9"/>
     </row>
     <row r="25" spans="1:26" ht="70.5" customHeight="1">
-      <c r="A25" s="83"/>
-      <c r="B25" s="83"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="89"/>
       <c r="C25" s="58" t="s">
         <v>13</v>
       </c>
@@ -3290,10 +3291,10 @@
       <c r="F25" s="12">
         <v>45534</v>
       </c>
-      <c r="G25" s="83"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="92"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="104"/>
       <c r="K25" s="15"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
@@ -3333,10 +3334,10 @@
       <c r="G26" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="79" t="s">
+      <c r="H26" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="I26" s="80"/>
+      <c r="I26" s="86"/>
       <c r="J26" s="14"/>
       <c r="K26" s="15" t="s">
         <v>30</v>
@@ -3358,10 +3359,10 @@
       <c r="Z26" s="9"/>
     </row>
     <row r="27" spans="1:26" ht="267" customHeight="1">
-      <c r="A27" s="95" t="s">
+      <c r="A27" s="92" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="93" t="s">
+      <c r="B27" s="87" t="s">
         <v>124</v>
       </c>
       <c r="C27" s="58" t="s">
@@ -3376,16 +3377,16 @@
       <c r="F27" s="12">
         <v>45190</v>
       </c>
-      <c r="G27" s="93" t="s">
+      <c r="G27" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="93" t="s">
+      <c r="H27" s="87" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="94" t="s">
+      <c r="I27" s="105" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="94" t="s">
+      <c r="J27" s="105" t="s">
         <v>127</v>
       </c>
       <c r="K27" s="35"/>
@@ -3406,8 +3407,8 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="42.75">
-      <c r="A28" s="83"/>
-      <c r="B28" s="83"/>
+      <c r="A28" s="89"/>
+      <c r="B28" s="89"/>
       <c r="C28" s="58" t="s">
         <v>13</v>
       </c>
@@ -3420,10 +3421,10 @@
       <c r="F28" s="12">
         <v>45400</v>
       </c>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
       <c r="K28" s="15"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
@@ -4446,7 +4447,7 @@
       <c r="Z51" s="9"/>
     </row>
     <row r="52" spans="1:26" s="74" customFormat="1" ht="84" customHeight="1">
-      <c r="A52" s="106" t="s">
+      <c r="A52" s="81" t="s">
         <v>318</v>
       </c>
       <c r="B52" s="75" t="s">
@@ -4458,10 +4459,10 @@
       </c>
       <c r="E52" s="17"/>
       <c r="F52" s="12"/>
-      <c r="G52" s="104" t="s">
+      <c r="G52" s="79" t="s">
         <v>320</v>
       </c>
-      <c r="H52" s="105" t="s">
+      <c r="H52" s="80" t="s">
         <v>321</v>
       </c>
       <c r="I52" s="13"/>
@@ -4566,7 +4567,7 @@
       <c r="Z54" s="9"/>
     </row>
     <row r="55" spans="1:26" ht="156.75">
-      <c r="A55" s="18" t="s">
+      <c r="A55" s="107" t="s">
         <v>277</v>
       </c>
       <c r="B55" s="10" t="s">
@@ -4700,7 +4701,7 @@
       <c r="Z57" s="9"/>
     </row>
     <row r="58" spans="1:26" ht="180" customHeight="1">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="107" t="s">
         <v>295</v>
       </c>
       <c r="B58" s="10" t="s">
@@ -4717,10 +4718,10 @@
       <c r="G58" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="H58" s="79" t="s">
+      <c r="H58" s="96" t="s">
         <v>299</v>
       </c>
-      <c r="I58" s="80"/>
+      <c r="I58" s="86"/>
       <c r="J58" s="13" t="s">
         <v>300</v>
       </c>
@@ -31287,22 +31288,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="I7:I10"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
     <mergeCell ref="H58:I58"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="H13:H15"/>
@@ -31316,6 +31301,22 @@
     <mergeCell ref="H27:H28"/>
     <mergeCell ref="I27:I28"/>
     <mergeCell ref="J27:J28"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D58" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -31404,9 +31405,7 @@
     <hyperlink ref="A57" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
     <hyperlink ref="E37" r:id="rId80" xr:uid="{BE8A3D1F-7217-4106-97EB-5926D8F6809C}"/>
     <hyperlink ref="A51" r:id="rId81" xr:uid="{4C5DAD40-0EE6-4723-9972-DED6C1C412C8}"/>
-    <hyperlink ref="A55" r:id="rId82" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="A58" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="A52" r:id="rId84" xr:uid="{AA4B0A3B-EFF0-43D2-8F6E-DAFE3F1EE47E}"/>
+    <hyperlink ref="A52" r:id="rId82" xr:uid="{AA4B0A3B-EFF0-43D2-8F6E-DAFE3F1EE47E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -31425,13 +31424,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="106" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
       <c r="A2" s="56"/>

--- a/Analyses/Partner-Analyses-Metadata.xlsx
+++ b/Analyses/Partner-Analyses-Metadata.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/otss1968_ox_ac_uk/Documents/Documents/GitHub/CCP/Analyses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A09F8105-248B-4F6F-99B9-1D3D44B1EB6A}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{356716B2-C3B1-498B-BBA3-AAA6A7893588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{498FAF26-2B1B-41B8-99D6-0A73A05B2EAC}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Partner Analyses" sheetId="1" r:id="rId1"/>
     <sheet name="Sub-processors" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partner Analyses'!$A$3:$Z$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partner Analyses'!$A$3:$Z$59</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="326">
   <si>
     <t>ISARIC Partner Analyses</t>
   </si>
@@ -1194,6 +1194,20 @@
   <si>
     <t>Zainab KA Alaraji, Alnahrain University College of medicine, Iraq.</t>
   </si>
+  <si>
+    <t>Bleeding risk in ECLS</t>
+  </si>
+  <si>
+    <t>External validation of a bleeding risk prediction model in COVID-19 patients receiving extracorporeal life support using the ISARIC dataset</t>
+  </si>
+  <si>
+    <t>Externally validate a simplified bleeding-risk prediction model for patients receiving ECLS/ECMO using international datasets.
+Assess the model’s performance and generalizability across different healthcare settings.
+Support future research on risk-based monitoring and management during ECLS.</t>
+  </si>
+  <si>
+    <t>Daisuke Kasugai, MD, PhD ), Nagoya University Hospital, Japan</t>
+  </si>
 </sst>
 </file>
 
@@ -1207,11 +1221,18 @@
     <numFmt numFmtId="168" formatCode="ddmmmyyyy"/>
     <numFmt numFmtId="169" formatCode="dmmmyyyy"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1701,73 +1722,70 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1776,25 +1794,25 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1803,187 +1821,194 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="36" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2203,7 +2228,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1006"/>
+  <dimension ref="A1:Z1007"/>
   <sheetFormatPr defaultColWidth="14.46484375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="44.265625" customWidth="1"/>
@@ -2219,18 +2244,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -2249,16 +2274,16 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="14.65" thickBot="1">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
+      <c r="A2" s="106"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -2348,10 +2373,10 @@
       <c r="G4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="85" t="s">
+      <c r="H4" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="86"/>
+      <c r="I4" s="85"/>
       <c r="J4" s="14" t="s">
         <v>18</v>
       </c>
@@ -2394,10 +2419,10 @@
       <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="85" t="s">
+      <c r="H5" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="86"/>
+      <c r="I5" s="85"/>
       <c r="J5" s="14" t="s">
         <v>18</v>
       </c>
@@ -2471,10 +2496,10 @@
       <c r="Z6" s="9"/>
     </row>
     <row r="7" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="98" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="58" t="s">
@@ -2489,13 +2514,13 @@
       <c r="F7" s="12">
         <v>44540</v>
       </c>
-      <c r="G7" s="90" t="s">
+      <c r="G7" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="91" t="s">
+      <c r="H7" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="91" t="s">
+      <c r="I7" s="89" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="19" t="s">
@@ -2519,8 +2544,8 @@
       <c r="Z7" s="9"/>
     </row>
     <row r="8" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A8" s="88"/>
-      <c r="B8" s="88"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="91"/>
       <c r="C8" s="58" t="s">
         <v>13</v>
       </c>
@@ -2533,9 +2558,9 @@
       <c r="F8" s="12">
         <v>44772</v>
       </c>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
       <c r="J8" s="19" t="s">
         <v>39</v>
       </c>
@@ -2557,8 +2582,8 @@
       <c r="Z8" s="9"/>
     </row>
     <row r="9" spans="1:26" ht="39.75" customHeight="1">
-      <c r="A9" s="88"/>
-      <c r="B9" s="88"/>
+      <c r="A9" s="91"/>
+      <c r="B9" s="91"/>
       <c r="C9" s="58" t="s">
         <v>13</v>
       </c>
@@ -2571,9 +2596,9 @@
       <c r="F9" s="12">
         <v>44817</v>
       </c>
-      <c r="G9" s="88"/>
-      <c r="H9" s="88"/>
-      <c r="I9" s="88"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
       <c r="J9" s="19" t="s">
         <v>39</v>
       </c>
@@ -2595,8 +2620,8 @@
       <c r="Z9" s="9"/>
     </row>
     <row r="10" spans="1:26" ht="47.25" customHeight="1">
-      <c r="A10" s="89"/>
-      <c r="B10" s="89"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="88"/>
       <c r="C10" s="58" t="s">
         <v>13</v>
       </c>
@@ -2609,9 +2634,9 @@
       <c r="F10" s="12">
         <v>45055</v>
       </c>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
       <c r="J10" s="19" t="s">
         <v>39</v>
       </c>
@@ -2733,10 +2758,10 @@
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A13" s="92" t="s">
+      <c r="A13" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="87" t="s">
+      <c r="B13" s="98" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="60" t="s">
@@ -2751,16 +2776,16 @@
       <c r="F13" s="12">
         <v>44671</v>
       </c>
-      <c r="G13" s="90" t="s">
+      <c r="G13" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="90" t="s">
+      <c r="H13" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="90" t="s">
+      <c r="I13" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="91" t="s">
+      <c r="J13" s="89" t="s">
         <v>62</v>
       </c>
       <c r="K13" s="28">
@@ -2783,8 +2808,8 @@
       <c r="Z13" s="9"/>
     </row>
     <row r="14" spans="1:26" s="56" customFormat="1" ht="66.75" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="102"/>
       <c r="C14" s="58" t="s">
         <v>13</v>
       </c>
@@ -2797,10 +2822,10 @@
       <c r="F14" s="12">
         <v>45072</v>
       </c>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="98"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="90"/>
       <c r="K14" s="28"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
@@ -2819,8 +2844,8 @@
       <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="78.75" customHeight="1">
-      <c r="A15" s="89"/>
-      <c r="B15" s="89"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="68" t="s">
         <v>13</v>
       </c>
@@ -2833,10 +2858,10 @@
       <c r="F15" s="71">
         <v>45981</v>
       </c>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
       <c r="K15" s="28"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -2905,10 +2930,10 @@
       <c r="Z16" s="9"/>
     </row>
     <row r="17" spans="1:26" ht="45" customHeight="1">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="98" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="58" t="s">
@@ -2923,7 +2948,7 @@
       <c r="F17" s="12">
         <v>44814</v>
       </c>
-      <c r="G17" s="90" t="s">
+      <c r="G17" s="86" t="s">
         <v>73</v>
       </c>
       <c r="H17" s="21" t="s">
@@ -2955,8 +2980,8 @@
       <c r="Z17" s="9"/>
     </row>
     <row r="18" spans="1:26" ht="102" customHeight="1">
-      <c r="A18" s="88"/>
-      <c r="B18" s="88"/>
+      <c r="A18" s="91"/>
+      <c r="B18" s="91"/>
       <c r="C18" s="58" t="s">
         <v>13</v>
       </c>
@@ -2969,7 +2994,7 @@
       <c r="F18" s="12">
         <v>45331</v>
       </c>
-      <c r="G18" s="88"/>
+      <c r="G18" s="91"/>
       <c r="H18" s="21" t="s">
         <v>74</v>
       </c>
@@ -2997,8 +3022,8 @@
       <c r="Z18" s="9"/>
     </row>
     <row r="19" spans="1:26" ht="78" customHeight="1">
-      <c r="A19" s="88"/>
-      <c r="B19" s="89"/>
+      <c r="A19" s="91"/>
+      <c r="B19" s="88"/>
       <c r="C19" s="58" t="s">
         <v>13</v>
       </c>
@@ -3011,7 +3036,7 @@
       <c r="F19" s="12">
         <v>45266</v>
       </c>
-      <c r="G19" s="88"/>
+      <c r="G19" s="91"/>
       <c r="H19" s="21" t="s">
         <v>79</v>
       </c>
@@ -3233,10 +3258,10 @@
       <c r="Z23" s="9"/>
     </row>
     <row r="24" spans="1:26" ht="124.5" customHeight="1">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="87" t="s">
+      <c r="B24" s="98" t="s">
         <v>111</v>
       </c>
       <c r="C24" s="61" t="s">
@@ -3251,14 +3276,14 @@
       <c r="F24" s="12">
         <v>44809</v>
       </c>
-      <c r="G24" s="90" t="s">
+      <c r="G24" s="86" t="s">
         <v>114</v>
       </c>
-      <c r="H24" s="99" t="s">
+      <c r="H24" s="92" t="s">
         <v>115</v>
       </c>
-      <c r="I24" s="100"/>
-      <c r="J24" s="101"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="94"/>
       <c r="K24" s="15"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
@@ -3277,8 +3302,8 @@
       <c r="Z24" s="9"/>
     </row>
     <row r="25" spans="1:26" ht="70.5" customHeight="1">
-      <c r="A25" s="89"/>
-      <c r="B25" s="89"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="88"/>
       <c r="C25" s="58" t="s">
         <v>13</v>
       </c>
@@ -3291,10 +3316,10 @@
       <c r="F25" s="12">
         <v>45534</v>
       </c>
-      <c r="G25" s="89"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="104"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="97"/>
       <c r="K25" s="15"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
@@ -3334,10 +3359,10 @@
       <c r="G26" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="96" t="s">
+      <c r="H26" s="84" t="s">
         <v>122</v>
       </c>
-      <c r="I26" s="86"/>
+      <c r="I26" s="85"/>
       <c r="J26" s="14"/>
       <c r="K26" s="15" t="s">
         <v>30</v>
@@ -3359,10 +3384,10 @@
       <c r="Z26" s="9"/>
     </row>
     <row r="27" spans="1:26" ht="267" customHeight="1">
-      <c r="A27" s="92" t="s">
+      <c r="A27" s="100" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="98" t="s">
         <v>124</v>
       </c>
       <c r="C27" s="58" t="s">
@@ -3377,16 +3402,16 @@
       <c r="F27" s="12">
         <v>45190</v>
       </c>
-      <c r="G27" s="87" t="s">
+      <c r="G27" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="87" t="s">
+      <c r="H27" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="105" t="s">
+      <c r="I27" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="105" t="s">
+      <c r="J27" s="99" t="s">
         <v>127</v>
       </c>
       <c r="K27" s="35"/>
@@ -3407,8 +3432,8 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="42.75">
-      <c r="A28" s="89"/>
-      <c r="B28" s="89"/>
+      <c r="A28" s="88"/>
+      <c r="B28" s="88"/>
       <c r="C28" s="58" t="s">
         <v>13</v>
       </c>
@@ -3421,10 +3446,10 @@
       <c r="F28" s="12">
         <v>45400</v>
       </c>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="88"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="88"/>
       <c r="K28" s="15"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
@@ -4484,25 +4509,25 @@
       <c r="Y52" s="9"/>
       <c r="Z52" s="9"/>
     </row>
-    <row r="53" spans="1:26" ht="57">
-      <c r="A53" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="C53" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="D53" s="45" t="s">
-        <v>226</v>
+    <row r="53" spans="1:26" s="82" customFormat="1" ht="84" customHeight="1">
+      <c r="A53" s="81" t="s">
+        <v>322</v>
+      </c>
+      <c r="B53" s="75" t="s">
+        <v>323</v>
+      </c>
+      <c r="C53" s="58"/>
+      <c r="D53" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="E53" s="17"/>
       <c r="F53" s="12"/>
-      <c r="G53" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="H53" s="13"/>
+      <c r="G53" s="109" t="s">
+        <v>324</v>
+      </c>
+      <c r="H53" s="80" t="s">
+        <v>325</v>
+      </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
       <c r="K53" s="15"/>
@@ -4523,32 +4548,26 @@
       <c r="Z53" s="9"/>
     </row>
     <row r="54" spans="1:26" ht="57">
-      <c r="A54" s="18" t="s">
-        <v>270</v>
+      <c r="A54" s="13" t="s">
+        <v>267</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C54" s="62"/>
+        <v>268</v>
+      </c>
+      <c r="C54" s="58" t="s">
+        <v>18</v>
+      </c>
       <c r="D54" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="E54" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="46"/>
+        <v>226</v>
+      </c>
+      <c r="E54" s="17"/>
+      <c r="F54" s="12"/>
       <c r="G54" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="J54" s="13" t="s">
-        <v>276</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
       <c r="K54" s="15"/>
       <c r="L54" s="9"/>
       <c r="M54" s="9"/>
@@ -4566,12 +4585,12 @@
       <c r="Y54" s="9"/>
       <c r="Z54" s="9"/>
     </row>
-    <row r="55" spans="1:26" ht="156.75">
-      <c r="A55" s="107" t="s">
-        <v>277</v>
+    <row r="55" spans="1:26" ht="57">
+      <c r="A55" s="18" t="s">
+        <v>270</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C55" s="62"/>
       <c r="D55" s="45" t="s">
@@ -4582,16 +4601,16 @@
       </c>
       <c r="F55" s="46"/>
       <c r="G55" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K55" s="15"/>
       <c r="L55" s="9"/>
@@ -4610,12 +4629,12 @@
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
     </row>
-    <row r="56" spans="1:26" ht="71.25">
-      <c r="A56" s="18" t="s">
-        <v>283</v>
+    <row r="56" spans="1:26" ht="156.75">
+      <c r="A56" s="83" t="s">
+        <v>277</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C56" s="62"/>
       <c r="D56" s="45" t="s">
@@ -4626,20 +4645,18 @@
       </c>
       <c r="F56" s="46"/>
       <c r="G56" s="13" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="K56" s="47">
-        <v>44213</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="K56" s="15"/>
       <c r="L56" s="9"/>
       <c r="M56" s="9"/>
       <c r="N56" s="9"/>
@@ -4656,12 +4673,12 @@
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
     </row>
-    <row r="57" spans="1:26" ht="96.75" customHeight="1">
+    <row r="57" spans="1:26" ht="71.25">
       <c r="A57" s="18" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C57" s="62"/>
       <c r="D57" s="45" t="s">
@@ -4672,18 +4689,20 @@
       </c>
       <c r="F57" s="46"/>
       <c r="G57" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="H57" s="19" t="s">
-        <v>292</v>
+        <v>285</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>286</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="K57" s="15"/>
+        <v>288</v>
+      </c>
+      <c r="K57" s="47">
+        <v>44213</v>
+      </c>
       <c r="L57" s="9"/>
       <c r="M57" s="9"/>
       <c r="N57" s="9"/>
@@ -4700,32 +4719,34 @@
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
     </row>
-    <row r="58" spans="1:26" ht="180" customHeight="1">
-      <c r="A58" s="107" t="s">
-        <v>295</v>
+    <row r="58" spans="1:26" ht="96.75" customHeight="1">
+      <c r="A58" s="18" t="s">
+        <v>289</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C58" s="62"/>
       <c r="D58" s="45" t="s">
         <v>272</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>297</v>
+        <v>13</v>
       </c>
       <c r="F58" s="46"/>
       <c r="G58" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="H58" s="96" t="s">
-        <v>299</v>
-      </c>
-      <c r="I58" s="86"/>
+        <v>291</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>293</v>
+      </c>
       <c r="J58" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="K58" s="48"/>
+        <v>294</v>
+      </c>
+      <c r="K58" s="15"/>
       <c r="L58" s="9"/>
       <c r="M58" s="9"/>
       <c r="N58" s="9"/>
@@ -4742,18 +4763,32 @@
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
     </row>
-    <row r="59" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A59" s="49"/>
-      <c r="B59" s="50"/>
-      <c r="C59" s="63"/>
-      <c r="D59" s="50"/>
-      <c r="E59" s="50"/>
-      <c r="F59" s="51"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="52"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="52"/>
-      <c r="K59" s="53"/>
+    <row r="59" spans="1:26" ht="180" customHeight="1">
+      <c r="A59" s="83" t="s">
+        <v>295</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59" s="62"/>
+      <c r="D59" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="F59" s="46"/>
+      <c r="G59" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="H59" s="84" t="s">
+        <v>299</v>
+      </c>
+      <c r="I59" s="85"/>
+      <c r="J59" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="K59" s="48"/>
       <c r="L59" s="9"/>
       <c r="M59" s="9"/>
       <c r="N59" s="9"/>
@@ -4771,7 +4806,7 @@
       <c r="Z59" s="9"/>
     </row>
     <row r="60" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A60" s="54"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="50"/>
       <c r="C60" s="63"/>
       <c r="D60" s="50"/>
@@ -4860,7 +4895,7 @@
       <c r="C63" s="63"/>
       <c r="D63" s="50"/>
       <c r="E63" s="50"/>
-      <c r="F63" s="55"/>
+      <c r="F63" s="51"/>
       <c r="G63" s="52"/>
       <c r="H63" s="52"/>
       <c r="I63" s="52"/>
@@ -9447,7 +9482,7 @@
       <c r="Z226" s="9"/>
     </row>
     <row r="227" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A227" s="9"/>
+      <c r="A227" s="54"/>
       <c r="B227" s="50"/>
       <c r="C227" s="63"/>
       <c r="D227" s="50"/>
@@ -31286,9 +31321,53 @@
       <c r="Y1006" s="9"/>
       <c r="Z1006" s="9"/>
     </row>
+    <row r="1007" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A1007" s="9"/>
+      <c r="B1007" s="50"/>
+      <c r="C1007" s="63"/>
+      <c r="D1007" s="50"/>
+      <c r="E1007" s="50"/>
+      <c r="F1007" s="55"/>
+      <c r="G1007" s="52"/>
+      <c r="H1007" s="52"/>
+      <c r="I1007" s="52"/>
+      <c r="J1007" s="52"/>
+      <c r="K1007" s="53"/>
+      <c r="L1007" s="9"/>
+      <c r="M1007" s="9"/>
+      <c r="N1007" s="9"/>
+      <c r="O1007" s="9"/>
+      <c r="P1007" s="9"/>
+      <c r="Q1007" s="9"/>
+      <c r="R1007" s="9"/>
+      <c r="S1007" s="9"/>
+      <c r="T1007" s="9"/>
+      <c r="U1007" s="9"/>
+      <c r="V1007" s="9"/>
+      <c r="W1007" s="9"/>
+      <c r="X1007" s="9"/>
+      <c r="Y1007" s="9"/>
+      <c r="Z1007" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="H59:I59"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="I13:I15"/>
@@ -31301,25 +31380,9 @@
     <mergeCell ref="H27:H28"/>
     <mergeCell ref="I27:I28"/>
     <mergeCell ref="J27:J28"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="H7:H10"/>
-    <mergeCell ref="I7:I10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D58" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D59" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Published,Awaiting publication,Analysis underway,Analysis completed,On hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -31400,12 +31463,13 @@
     <hyperlink ref="C47" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
     <hyperlink ref="A48" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
     <hyperlink ref="A49" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="A54" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="A56" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="A57" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="A55" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="A57" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="A58" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
     <hyperlink ref="E37" r:id="rId80" xr:uid="{BE8A3D1F-7217-4106-97EB-5926D8F6809C}"/>
     <hyperlink ref="A51" r:id="rId81" xr:uid="{4C5DAD40-0EE6-4723-9972-DED6C1C412C8}"/>
     <hyperlink ref="A52" r:id="rId82" xr:uid="{AA4B0A3B-EFF0-43D2-8F6E-DAFE3F1EE47E}"/>
+    <hyperlink ref="A53" r:id="rId83" xr:uid="{F3A48EC8-A8EC-4902-BD1F-CB107258933F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -31424,13 +31488,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="108" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
       <c r="A2" s="56"/>
